--- a/content/research/cars-research-2026-10.xlsx
+++ b/content/research/cars-research-2026-10.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1033" uniqueCount="527">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1313" uniqueCount="622">
   <si>
     <t>بحث أسعار وصور سيارات المعرض — تشرين الأول 2026</t>
   </si>
@@ -31,7 +31,7 @@
     <t>• ورقة «الأسعار»: لكل سيارة من الـ 34 بالملف، سعرها بسوق العراق من إعلانات حقيقية (الوسيط، أقل وأعلى سعر، عدد الإعلانات) مع روابط المصادر، والسعر المقترح بالدينار.</t>
   </si>
   <si>
-    <t>• ورقة «الصور»: 70 صورة حقيقية مرخّصة من ويكيميديا كومنز لنفس الموديلات والأجيال، مع اسم المصوّر ونوع الرخصة ونص الإسناد الجاهز.</t>
+    <t>• ورقة «الصور»: 98 صورة حقيقية مرخّصة من ويكيميديا كومنز لنفس الموديلات والأجيال (بحث 26 تشرين الأول 2026، مع التحقق من الرخصة والمقاس عبر Commons API)، مع اسم المصوّر ونوع الرخصة ونص الإسناد الجاهز. الصور الرسمية لمواقع الشركات لم تُستخدم لأن شروطها تحصرها بالاستخدام الصحفي.</t>
   </si>
   <si>
     <t>• ورقة «الوكلاء والتمويل»: الوكلاء الرسميون للماركات الصينية بالعراق وعروض التمويل المصرفية المنشورة.</t>
@@ -665,253 +665,787 @@
     <t>Toyota Camry 2024</t>
   </si>
   <si>
-    <t>2023 Toyota Camry XSE, front right, 08-30-2026.jpg</t>
+    <t>2022 Toyota Camry SE Standard Package in Celestial Silver Metallic, Front Left.jpg</t>
+  </si>
+  <si>
+    <t>Elise240SX</t>
+  </si>
+  <si>
+    <t>CC BY-SA 4.0</t>
+  </si>
+  <si>
+    <t>الصورة: Elise240SX / Wikimedia Commons — CC BY-SA 4.0</t>
+  </si>
+  <si>
+    <t>فتح</t>
+  </si>
+  <si>
+    <t>تحميل</t>
+  </si>
+  <si>
+    <t>car-001-1.webp</t>
+  </si>
+  <si>
+    <t>2022 SE, same XV70 2021+ facelift as 2024 SE. Color differs from requested red.</t>
+  </si>
+  <si>
+    <t>2022 Toyota Camry SE Standard Package in Celestial Silver Metallic, Rear Left.jpg</t>
+  </si>
+  <si>
+    <t>car-001-2.webp</t>
+  </si>
+  <si>
+    <t>Same car as car-001-1. Color differs from requested red.</t>
+  </si>
+  <si>
+    <t>24 Toyota Camry SE.jpg</t>
+  </si>
+  <si>
+    <t>HJUdall</t>
+  </si>
+  <si>
+    <t>CC0</t>
+  </si>
+  <si>
+    <t>HJUdall / Wikimedia Commons (CC0)</t>
+  </si>
+  <si>
+    <t>car-001-3.webp</t>
+  </si>
+  <si>
+    <t>Exact 2024 SE. Color and angle not stated; check visually. Shot on a dealer lot by a Commons user (photo is the uploader's own work, not taken from a dealer website).</t>
+  </si>
+  <si>
+    <t>Toyota Corolla 2023</t>
+  </si>
+  <si>
+    <t>2024 Toyota Corolla LE in Classic Silver Metallic, front right.jpg</t>
+  </si>
+  <si>
+    <t>Mr.choppers</t>
+  </si>
+  <si>
+    <t>CC BY-SA 3.0</t>
+  </si>
+  <si>
+    <t>الصورة: Mr.choppers / Wikimedia Commons — CC BY-SA 3.0</t>
+  </si>
+  <si>
+    <t>car-002-1.webp</t>
+  </si>
+  <si>
+    <t>2024 LE, same E210 2023 facelift. LE front bumper differs from SE/XSE sport fascia. Color differs from requested white.</t>
+  </si>
+  <si>
+    <t>2025 Toyota Corolla LE ice cap.jpg</t>
+  </si>
+  <si>
+    <t>Rachelhoots</t>
+  </si>
+  <si>
+    <t>الصورة: Rachelhoots / Wikimedia Commons — CC BY-SA 4.0</t>
+  </si>
+  <si>
+    <t>car-002-2.webp</t>
+  </si>
+  <si>
+    <t>2025 LE, same 2023+ facelift. White as requested; angle not stated, check visually.</t>
+  </si>
+  <si>
+    <t>24 Toyota Corolla XSE.jpg</t>
+  </si>
+  <si>
+    <t>car-002-3.webp</t>
+  </si>
+  <si>
+    <t>2024 XSE shares the SE sport front fascia; nearest match to SE trim found. Color/angle not stated; check visually.</t>
+  </si>
+  <si>
+    <t>Toyota Land Cruiser 2026</t>
+  </si>
+  <si>
+    <t>Moscow, Toyota Land Cruiser black, Sept 2025 01.jpg</t>
+  </si>
+  <si>
+    <t>Retired electrician</t>
+  </si>
+  <si>
+    <t>Retired electrician / Wikimedia Commons (CC0)</t>
+  </si>
+  <si>
+    <t>car-003-1.webp</t>
+  </si>
+  <si>
+    <t>J300 in black (category Toyota Land Cruiser (J300)); street photo in Moscow, not GCC GXR spec - grille/trim may differ. Angle not stated; check visually.</t>
+  </si>
+  <si>
+    <t>2021 Toyota Land Cruiser 300 (Russia) rear view.png</t>
+  </si>
+  <si>
+    <t>Авто Плюс Новости</t>
+  </si>
+  <si>
+    <t>CC BY 3.0</t>
+  </si>
+  <si>
+    <t>الصورة: Авто Плюс Новости / Wikimedia Commons — CC BY 3.0</t>
+  </si>
+  <si>
+    <t>car-003-2.webp</t>
+  </si>
+  <si>
+    <t>Russian-market 2021 J300. Author is a video channel; likely a video frame - check for channel logo/text overlay before use.</t>
+  </si>
+  <si>
+    <t>2021 Toyota Land Cruiser 300 (Colombia) interior.png</t>
+  </si>
+  <si>
+    <t>Autosdeprimera</t>
+  </si>
+  <si>
+    <t>الصورة: Autosdeprimera / Wikimedia Commons — CC BY 3.0</t>
+  </si>
+  <si>
+    <t>car-003-3.webp</t>
+  </si>
+  <si>
+    <t>Colombian-market 2021 J300 interior. Likely a video frame - check for logo/text overlay.</t>
+  </si>
+  <si>
+    <t>Toyota Land Cruiser Prado 2023</t>
+  </si>
+  <si>
+    <t>Toyota Land Cruiser Prado J150 3.0 VX 2022 (2).jpg</t>
+  </si>
+  <si>
+    <t>Ethan Llamas</t>
+  </si>
+  <si>
+    <t>الصورة: Ethan Llamas / Wikimedia Commons — CC BY-SA 4.0</t>
+  </si>
+  <si>
+    <t>car-004-1.webp</t>
+  </si>
+  <si>
+    <t>2022 Prado J150 final facelift (Philippine 3.0 VX diesel), same body as GCC 2023 TXL. Check whether straight-on front or three-quarter.</t>
+  </si>
+  <si>
+    <t>Toyota Land Cruiser Prado J150 3.0 VX 2022 (1).jpg</t>
+  </si>
+  <si>
+    <t>car-004-2.webp</t>
+  </si>
+  <si>
+    <t>Same car/series as car-004-1.</t>
+  </si>
+  <si>
+    <t>Toyota Land Cruiser Prado J150 LWB facelift Sanming 01 2023-02-16.jpg</t>
+  </si>
+  <si>
+    <t>JamesYoung8167</t>
+  </si>
+  <si>
+    <t>الصورة: JamesYoung8167 / Wikimedia Commons — CC BY-SA 4.0</t>
+  </si>
+  <si>
+    <t>car-004-3.webp</t>
+  </si>
+  <si>
+    <t>J150 5-door facelift photographed in China. Confirm it is the 2017.9+ final facelift face, not the 2013 one.</t>
+  </si>
+  <si>
+    <t>Kia K5 2024</t>
+  </si>
+  <si>
+    <t>KIA K5 EXTERIOR China(1).jpg</t>
+  </si>
+  <si>
+    <t>Dinkun Chen</t>
+  </si>
+  <si>
+    <t>الصورة: Dinkun Chen / Wikimedia Commons — CC BY-SA 4.0</t>
+  </si>
+  <si>
+    <t>car-005-1.webp</t>
+  </si>
+  <si>
+    <t>China-market K5 (DL3). Pre-facelift vs facelift is NOT stated in metadata and could not be confirmed without viewing; check the headlights/DRL signature. No Korean-market GT-Line found on Commons.</t>
+  </si>
+  <si>
+    <t>KIA K5 EXTERIOR China(2).jpg</t>
+  </si>
+  <si>
+    <t>car-005-2.webp</t>
+  </si>
+  <si>
+    <t>Same series/author as car-005-1; check angle and facelift status.</t>
+  </si>
+  <si>
+    <t>KIA K5 INTERIOR China.jpg</t>
+  </si>
+  <si>
+    <t>car-005-3.webp</t>
+  </si>
+  <si>
+    <t>China-market K5 interior; dashboard layout may differ from Korean GT-Line.</t>
+  </si>
+  <si>
+    <t>Kia Sportage 2023</t>
+  </si>
+  <si>
+    <t>2023 Kia Sportage LX in Gravity Grey, Front Left, 05-22-2022.jpg</t>
+  </si>
+  <si>
+    <t>car-006-1.webp</t>
+  </si>
+  <si>
+    <t>2023 NQ5 pre-facelift, North American long-wheelbase body (same body as Korean market). LX trim, not GT-Line. Color differs from requested black.</t>
+  </si>
+  <si>
+    <t>2022 KIA Sportage GT-Line - 1598cc 1.6 (148PS) Petrol - Orange Fusion - 02-2025, Front.jpg</t>
+  </si>
+  <si>
+    <t>Harvey Bold</t>
+  </si>
+  <si>
+    <t>Harvey Bold / Wikimedia Commons (CC0)</t>
+  </si>
+  <si>
+    <t>car-006-2.webp</t>
+  </si>
+  <si>
+    <t>2022 GT-Line 1.6T, NQ5 pre-facelift. European market: shorter body than the Korean NQ5, rear doors/rear end differ. Color differs from black.</t>
+  </si>
+  <si>
+    <t>2022 KIA Sportage GT-Line - 1598cc 1.6 (148PS) Petrol - Orange Fusion - 02-2025, Rear.jpg</t>
+  </si>
+  <si>
+    <t>car-006-3.webp</t>
+  </si>
+  <si>
+    <t>Same car as car-006-2; European short-body NQ5.</t>
+  </si>
+  <si>
+    <t>2024 Kia Sorento X-Line SX Prestige (facelift), front 12.20.24.jpg</t>
+  </si>
+  <si>
+    <t>Kevauto</t>
+  </si>
+  <si>
+    <t>الصورة: Kevauto / Wikimedia Commons — CC BY-SA 4.0</t>
+  </si>
+  <si>
+    <t>car-007-1.webp</t>
+  </si>
+  <si>
+    <t>MQ4 facelift (stated in title), US 2024 X-Line SX Prestige. Middle East 3.5 V6 shares the facelift body.</t>
+  </si>
+  <si>
+    <t>2024 Kia Sorento X-Line SX Prestige (facelift), rear 12.20.24.jpg</t>
+  </si>
+  <si>
+    <t>car-007-2.webp</t>
+  </si>
+  <si>
+    <t>Same car as car-007-1.</t>
+  </si>
+  <si>
+    <t>2024 Kia Sorento LX in Gravity Grey, front left, 2024-07-21.jpg</t>
+  </si>
+  <si>
+    <t>car-007-3.webp</t>
+  </si>
+  <si>
+    <t>2024 Canadian LX in grey (requested color). Facelift not stated in metadata; 2024 model year in Canada should be the facelift but confirm visually.</t>
+  </si>
+  <si>
+    <t>0 Hyundai Sonata (DN8) sensuous 1.jpg</t>
+  </si>
+  <si>
+    <t>Benespit</t>
+  </si>
+  <si>
+    <t>الصورة: Benespit / Wikimedia Commons — CC BY-SA 4.0</t>
+  </si>
+  <si>
+    <t>car-008-1.webp</t>
+  </si>
+  <si>
+    <t>DN8 'Sensuous' (the Korean name of the launch-era turbo trim), so pre-facelift; confirm the front visually. Check angle.</t>
+  </si>
+  <si>
+    <t>0 Hyundai Sonata (DN8) sensuous 2.jpg</t>
+  </si>
+  <si>
+    <t>car-008-2.webp</t>
+  </si>
+  <si>
+    <t>Same series as car-008-1. Check angle.</t>
+  </si>
+  <si>
+    <t>23 Hyundai Sonata SE.jpg</t>
+  </si>
+  <si>
+    <t>car-008-3.webp</t>
+  </si>
+  <si>
+    <t>2023 US Sonata SE = DN8 pre-facelift (US facelift came for 2024). Exactly 1600 px wide - at the minimum. Shot on a dealer lot by a Commons user.</t>
+  </si>
+  <si>
+    <t>Hyundai Tucson NX4 SWB Serenity White Pearl (1).jpg</t>
+  </si>
+  <si>
+    <t>Damian B Oh</t>
+  </si>
+  <si>
+    <t>الصورة: Damian B Oh / Wikimedia Commons — CC BY-SA 4.0</t>
+  </si>
+  <si>
+    <t>car-009-1.webp</t>
+  </si>
+  <si>
+    <t>NX4 pre-facelift look (file not labelled facelift; the same uploader labels facelift cars separately). Uploader labels it SWB (short wheelbase); check against GCC body. Angle not stated.</t>
+  </si>
+  <si>
+    <t>Hyundai Tucson NX4 SWB Serenity White Pearl (2).jpg</t>
+  </si>
+  <si>
+    <t>car-009-2.webp</t>
+  </si>
+  <si>
+    <t>Same car as car-009-1. Check angle.</t>
+  </si>
+  <si>
+    <t>Hyundai Tucson NX4 SWB Serenity White Pearl (3).jpg</t>
+  </si>
+  <si>
+    <t>car-009-3.webp</t>
+  </si>
+  <si>
+    <t>Hyundai Elantra 2023</t>
+  </si>
+  <si>
+    <t>2020 Beijing-Hyundai Elantra (front).jpg</t>
+  </si>
+  <si>
+    <t>User3204</t>
+  </si>
+  <si>
+    <t>الصورة: User3204 / Wikimedia Commons — CC BY-SA 4.0</t>
+  </si>
+  <si>
+    <t>car-010-1.webp</t>
+  </si>
+  <si>
+    <t>2020 CN7 = pre-facelift. China-market (Beijing-Hyundai) car, same CN7 design. Color differs from requested silver.</t>
+  </si>
+  <si>
+    <t>2020 Beijing-Hyundai Elantra (rear).jpg</t>
+  </si>
+  <si>
+    <t>car-010-2.webp</t>
+  </si>
+  <si>
+    <t>Same car as car-010-1.</t>
+  </si>
+  <si>
+    <t>Nissan Altima 2023</t>
+  </si>
+  <si>
+    <t>2024 Nissan Altima SR, front left, 05-05-2025.jpg</t>
   </si>
   <si>
     <t>MercurySable99</t>
   </si>
   <si>
-    <t>CC BY-SA 4.0</t>
-  </si>
-  <si>
     <t>الصورة: MercurySable99 / Wikimedia Commons — CC BY-SA 4.0</t>
   </si>
   <si>
-    <t>فتح</t>
-  </si>
-  <si>
-    <t>تحميل</t>
-  </si>
-  <si>
-    <t>car-001-1.webp</t>
-  </si>
-  <si>
-    <t>XV70 facelift, US; front 3/4</t>
-  </si>
-  <si>
-    <t>Toyota Camry (XV70) XSE.jpg</t>
-  </si>
-  <si>
-    <t>Benespit</t>
-  </si>
-  <si>
-    <t>الصورة: Benespit / Wikimedia Commons — CC BY-SA 4.0</t>
-  </si>
-  <si>
-    <t>car-001-2.webp</t>
-  </si>
-  <si>
-    <t>XV70 XSE</t>
-  </si>
-  <si>
-    <t>Toyota Corolla 2023</t>
-  </si>
-  <si>
-    <t>22 Toyota Corolla SE.jpg</t>
-  </si>
-  <si>
-    <t>HJUdall</t>
-  </si>
-  <si>
-    <t>CC0</t>
-  </si>
-  <si>
-    <t>HJUdall / Wikimedia Commons (CC0)</t>
-  </si>
-  <si>
-    <t>car-002-1.webp</t>
-  </si>
-  <si>
-    <t>E210 sedan SE, US</t>
-  </si>
-  <si>
-    <t>20 Toyota Corolla SE.jpg</t>
-  </si>
-  <si>
-    <t>car-002-2.webp</t>
-  </si>
-  <si>
-    <t>Toyota Land Cruiser 2026</t>
-  </si>
-  <si>
-    <t>TOYOTA LAND CRUISER (J300) China (5).jpg</t>
-  </si>
-  <si>
-    <t>Dinkun Chen</t>
-  </si>
-  <si>
-    <t>الصورة: Dinkun Chen / Wikimedia Commons — CC BY-SA 4.0</t>
-  </si>
-  <si>
-    <t>car-003-1.webp</t>
-  </si>
-  <si>
-    <t>LC300, Shenzhen</t>
-  </si>
-  <si>
-    <t>2021 Toyota Land Cruieser 300 ZX.jpg</t>
-  </si>
-  <si>
-    <t>TTTNIS</t>
-  </si>
-  <si>
-    <t>TTTNIS / Wikimedia Commons (CC0)</t>
-  </si>
-  <si>
-    <t>car-003-2.webp</t>
-  </si>
-  <si>
-    <t>LC300 ZX (Japan)</t>
-  </si>
-  <si>
-    <t>TOYOTA LAND CRUISER (J300) China.jpg</t>
-  </si>
-  <si>
-    <t>car-003-3.webp</t>
-  </si>
-  <si>
-    <t>LC300, Greater Bay Area Auto Show 2023</t>
-  </si>
-  <si>
-    <t>Toyota Land Cruiser Prado 2023</t>
-  </si>
-  <si>
-    <t>Toyota Land Cruiser Prado 4.0 VXL 2019 (52600778647).jpg</t>
-  </si>
-  <si>
-    <t>RL GNZLZ (Flickr)</t>
-  </si>
-  <si>
-    <t>CC BY-SA 2.0</t>
-  </si>
-  <si>
-    <t>الصورة: RL GNZLZ (Flickr) / Wikimedia Commons — CC BY-SA 2.0</t>
-  </si>
-  <si>
-    <t>car-004-1.webp</t>
-  </si>
-  <si>
-    <t>J150 facelift 4.0 VXL</t>
-  </si>
-  <si>
-    <t>Toyota Land Cruiser Prado RX, Rear Right, 08-22-2021.jpg</t>
-  </si>
-  <si>
-    <t>Elise240SX</t>
-  </si>
-  <si>
-    <t>الصورة: Elise240SX / Wikimedia Commons — CC BY-SA 4.0</t>
-  </si>
-  <si>
-    <t>car-004-2.webp</t>
-  </si>
-  <si>
-    <t>J150, rear</t>
-  </si>
-  <si>
-    <t>Kia K5 2024</t>
-  </si>
-  <si>
-    <t>2021 Kia K5 GT-Line, front left, 09-09-2023.jpg</t>
-  </si>
-  <si>
-    <t>car-005-1.webp</t>
-  </si>
-  <si>
-    <t>DL3 GT-Line, grey</t>
-  </si>
-  <si>
-    <t>2022 Kia K5 GT-Line in Pacific Blue, Rear Right, 09-05-2022.jpg</t>
-  </si>
-  <si>
-    <t>car-005-2.webp</t>
-  </si>
-  <si>
-    <t>DL3 GT-Line, blue, rear</t>
-  </si>
-  <si>
-    <t>Kia Sportage 2023</t>
-  </si>
-  <si>
-    <t>2022 Kia Sportage GT-Line ISG.jpg</t>
-  </si>
-  <si>
-    <t>Calreyn88</t>
-  </si>
-  <si>
-    <t>الصورة: Calreyn88 / Wikimedia Commons — CC BY-SA 4.0</t>
-  </si>
-  <si>
-    <t>car-006-1.webp</t>
-  </si>
-  <si>
-    <t>NQ5 GT-Line (UK)</t>
-  </si>
-  <si>
-    <t>2021 Kia Sportage GT-Line ISG.jpg</t>
-  </si>
-  <si>
-    <t>car-006-2.webp</t>
-  </si>
-  <si>
-    <t>2024 Kia Sorento X-Line SX Prestige (facelift), front 12.20.24.jpg</t>
-  </si>
-  <si>
-    <t>Kevauto</t>
-  </si>
-  <si>
-    <t>الصورة: Kevauto / Wikimedia Commons — CC BY-SA 4.0</t>
-  </si>
-  <si>
-    <t>car-007-1.webp</t>
-  </si>
-  <si>
-    <t>MQ4 facelift</t>
-  </si>
-  <si>
-    <t>2024 Kia Sorento X-Line SX Prestige (facelift), rear 12.20.24.jpg</t>
-  </si>
-  <si>
-    <t>car-007-2.webp</t>
-  </si>
-  <si>
-    <t>MQ4 facelift, rear</t>
-  </si>
-  <si>
-    <t>2021 Hyundai Sonata 2.5 MPi black front view in Brunei.jpg</t>
-  </si>
-  <si>
-    <t>AIMHO'S REBELLION 8490s</t>
-  </si>
-  <si>
-    <t>الصورة: AIMHO'S REBELLION 8490s / Wikimedia Commons — CC BY-SA 4.0</t>
-  </si>
-  <si>
-    <t>car-008-1.webp</t>
-  </si>
-  <si>
-    <t>DN8 2.5 MPi, black</t>
-  </si>
-  <si>
-    <t>2021 Hyundai Sonata 2.5 MPi black rear view in Brunei.jpg</t>
-  </si>
-  <si>
-    <t>car-008-2.webp</t>
-  </si>
-  <si>
-    <t>DN8, black, rear</t>
-  </si>
-  <si>
-    <t>2021 Hyundai Sonata 2.5 MPi black interior view in Brunei.jpg</t>
-  </si>
-  <si>
-    <t>car-008-3.webp</t>
-  </si>
-  <si>
-    <t>DN8 interior</t>
-  </si>
-  <si>
-    <t>Hyundai Tucson (NX4, SWB) Facelift Sindelfingen 2024 IMG 9230.jpg</t>
+    <t>car-011-1.webp</t>
+  </si>
+  <si>
+    <t>2024 = same L34 facelift as 2023. SR trim (sportier bumpers/wheels than SV).</t>
+  </si>
+  <si>
+    <t>2024 Nissan Altima SR, rear right, 05-05-2025.jpg</t>
+  </si>
+  <si>
+    <t>car-011-2.webp</t>
+  </si>
+  <si>
+    <t>Same car as car-011-1.</t>
+  </si>
+  <si>
+    <t>2023 Nissan Altima interior.jpg</t>
+  </si>
+  <si>
+    <t>deathpallie325</t>
+  </si>
+  <si>
+    <t>الصورة: deathpallie325 / Wikimedia Commons — CC BY-SA 4.0</t>
+  </si>
+  <si>
+    <t>car-011-3.webp</t>
+  </si>
+  <si>
+    <t>2023 Altima SR dashboard (facelift).</t>
+  </si>
+  <si>
+    <t>Nissan Patrol 2026</t>
+  </si>
+  <si>
+    <t>Nissan Patrol 2025 Y63.jpg</t>
+  </si>
+  <si>
+    <t>ToyGTone</t>
+  </si>
+  <si>
+    <t>ToyGTone / Wikimedia Commons (CC0)</t>
+  </si>
+  <si>
+    <t>car-012-1.webp</t>
+  </si>
+  <si>
+    <t>2025 Patrol LE Platinum V6T (Y63) photographed in a Nissan showroom in Bahrain (GCC spec, exact trim). Photo is the uploader's own work. Color/angle not stated.</t>
+  </si>
+  <si>
+    <t>Nissan Patrol Y63 3.5 V6T LE Granite Black - rear.jpg</t>
+  </si>
+  <si>
+    <t>car-012-2.webp</t>
+  </si>
+  <si>
+    <t>Philippine-market Y63 3.5 V6T LE in black.</t>
+  </si>
+  <si>
+    <t>Nissan Patrol Y63 3.5 V6T LE interior view.jpg</t>
+  </si>
+  <si>
+    <t>car-012-3.webp</t>
+  </si>
+  <si>
+    <t>Philippine-market Y63 LE interior.</t>
+  </si>
+  <si>
+    <t>2024 Nissan Versa front view.jpg</t>
+  </si>
+  <si>
+    <t>Deathpallie325</t>
+  </si>
+  <si>
+    <t>CC BY 4.0</t>
+  </si>
+  <si>
+    <t>الصورة: Deathpallie325 / Wikimedia Commons — CC BY 4.0</t>
+  </si>
+  <si>
+    <t>car-013-1.webp</t>
+  </si>
+  <si>
+    <t>2024 US Versa SR (N18, same car as GCC Sunny). US Versa had a 2023 refresh; confirm the GCC 2024 Sunny uses the same front.</t>
+  </si>
+  <si>
+    <t>23 Nissan Versa SR.jpg</t>
+  </si>
+  <si>
+    <t>car-013-2.webp</t>
+  </si>
+  <si>
+    <t>2023 US Versa SR. Shot on a dealer lot by a Commons user.</t>
+  </si>
+  <si>
+    <t>2023 Nissan Versa (N18) IMG 3105.jpg</t>
+  </si>
+  <si>
+    <t>Alexander Migl</t>
+  </si>
+  <si>
+    <t>الصورة: Alexander Migl / Wikimedia Commons — CC BY-SA 4.0</t>
+  </si>
+  <si>
+    <t>car-013-3.webp</t>
+  </si>
+  <si>
+    <t>2023 Versa (N18). Check angle.</t>
+  </si>
+  <si>
+    <t>Chevrolet Malibu 2023</t>
+  </si>
+  <si>
+    <t>2023 Chevrolet Malibu 1LT in Sterling Grey Metallic, front left, 2024-11-14.jpg</t>
+  </si>
+  <si>
+    <t>car-014-1.webp</t>
+  </si>
+  <si>
+    <t>Exact model year, LT trim (1LT), requested color. 9th gen facelift.</t>
+  </si>
+  <si>
+    <t>2024 Chevrolet Malibu 1LT in Sterling Grey Metallic, rear right, 2024-03-31.jpg</t>
+  </si>
+  <si>
+    <t>car-014-2.webp</t>
+  </si>
+  <si>
+    <t>2024 1LT, identical body to 2023.</t>
+  </si>
+  <si>
+    <t>Chevrolet Tahoe 2023</t>
+  </si>
+  <si>
+    <t>2022 Chevrolet Tahoe RST, front 3.7.22.jpg</t>
+  </si>
+  <si>
+    <t>car-015-1.webp</t>
+  </si>
+  <si>
+    <t>2022 Tahoe = 5th gen (GMT T1XX) pre-facelift, same as 2023. RST trim (body-colour grille) rather than LT.</t>
+  </si>
+  <si>
+    <t>2022 Chevrolet Tahoe RST, rear 3.7.22.jpg</t>
+  </si>
+  <si>
+    <t>car-015-2.webp</t>
+  </si>
+  <si>
+    <t>Same car as car-015-1.</t>
+  </si>
+  <si>
+    <t>Chevrolet Tahoe GMT1UC 5.3 Z71 V8 Black.jpg</t>
+  </si>
+  <si>
+    <t>car-015-3.webp</t>
+  </si>
+  <si>
+    <t>5th gen pre-facelift 5.3 V8 in requested black; Z71 trim (off-road front bumper differs from LT). Philippine market.</t>
+  </si>
+  <si>
+    <t>2024 Lexus ES Sedan.jpg</t>
+  </si>
+  <si>
+    <t>Wlb5V</t>
+  </si>
+  <si>
+    <t>الصورة: Wlb5V / Wikimedia Commons — CC BY-SA 4.0</t>
+  </si>
+  <si>
+    <t>car-016-1.webp</t>
+  </si>
+  <si>
+    <t>2024 ES = XZ10 2022+ facelift. Photographed outside a Lexus dealership by a Commons user. Check angle/color.</t>
+  </si>
+  <si>
+    <t>Lexus ES 300h (2023) (54742901894).jpg</t>
+  </si>
+  <si>
+    <t>Charles from Port Chester, New York</t>
+  </si>
+  <si>
+    <t>Charles from Port Chester, New York / Wikimedia Commons (CC0)</t>
+  </si>
+  <si>
+    <t>car-016-2.webp</t>
+  </si>
+  <si>
+    <t>2023 ES 300h - same facelift body as ES 350 (badging differs). Flickr import.</t>
+  </si>
+  <si>
+    <t>2024 Lexus ES in Sunlit Green.jpg</t>
+  </si>
+  <si>
+    <t>car-016-3.webp</t>
+  </si>
+  <si>
+    <t>2024 ES facelift. Color differs from requested white.</t>
+  </si>
+  <si>
+    <t>2023 Lexus RX 350 Premium Plus in Matador Red Mica, front left.jpg</t>
+  </si>
+  <si>
+    <t>car-017-1.webp</t>
+  </si>
+  <si>
+    <t>2023 RX 350 2.4T AWD (AL30). Color differs from requested blue; no blue AL30 found.</t>
+  </si>
+  <si>
+    <t>2023 Lexus RX 350 Premium Plus in Matador Red Mica, rear left.jpg</t>
+  </si>
+  <si>
+    <t>car-017-2.webp</t>
+  </si>
+  <si>
+    <t>Same car as car-017-1.</t>
+  </si>
+  <si>
+    <t>23 Lexus RX 350 Premium.jpg</t>
+  </si>
+  <si>
+    <t>car-017-3.webp</t>
+  </si>
+  <si>
+    <t>2023 RX 350 (AL30). Shot on a dealer lot by a Commons user. Check color/angle.</t>
+  </si>
+  <si>
+    <t>Mercedes C 300 2024</t>
+  </si>
+  <si>
+    <t>Mercedes-Benz C 300 d AMG Line (W 206) – f 10032024.jpg</t>
+  </si>
+  <si>
+    <t>© M 93</t>
+  </si>
+  <si>
+    <t>CC BY-SA 3.0 de</t>
+  </si>
+  <si>
+    <t>الصورة: © M 93 / Wikimedia Commons — CC BY-SA 3.0 de</t>
+  </si>
+  <si>
+    <t>car-018-1.webp</t>
+  </si>
+  <si>
+    <t>W206 C 300 d AMG Line (European diesel) - same body/AMG Line styling as US C 300; badge differs.</t>
+  </si>
+  <si>
+    <t>Mercedes-Benz C 300 d AMG Line (W 206) – h 10032024.jpg</t>
+  </si>
+  <si>
+    <t>car-018-2.webp</t>
+  </si>
+  <si>
+    <t>Same car as car-018-1. Rear badge reads 300 d.</t>
+  </si>
+  <si>
+    <t>Mercedes-Benz W206 C 300 4MATIC AMG Line Polar White (4).jpg</t>
+  </si>
+  <si>
+    <t>car-018-3.webp</t>
+  </si>
+  <si>
+    <t>W206 C 300 4MATIC AMG Line in requested white (Korean market). Check angle; other numbers in the same series give more angles.</t>
+  </si>
+  <si>
+    <t>Mercedes GLE 450 2026</t>
+  </si>
+  <si>
+    <t>Mercedes-Benz GLE AMG Line (V 167, Facelift) – f 14042024.jpg</t>
+  </si>
+  <si>
+    <t>car-019-1.webp</t>
+  </si>
+  <si>
+    <t>V167 facelift (stated in title), AMG Line, European market. Engine variant not stated.</t>
+  </si>
+  <si>
+    <t>Mercedes-Benz GLE AMG Line (V 167, Facelift) – h 14042024.jpg</t>
+  </si>
+  <si>
+    <t>car-019-2.webp</t>
+  </si>
+  <si>
+    <t>Same car as car-019-1.</t>
+  </si>
+  <si>
+    <t>Mercedes-Benz GLE 450 4MATIC (W167, 2026) (55211989821).jpg</t>
+  </si>
+  <si>
+    <t>car-019-3.webp</t>
+  </si>
+  <si>
+    <t>2026 GLE 450 4MATIC = facelift, exact engine (3.0 turbo I6). Flickr import. Check angle/color.</t>
+  </si>
+  <si>
+    <t>BMW 520i 2026</t>
+  </si>
+  <si>
+    <t>BMW G60 520i M Sport Alpine White (1).jpg</t>
+  </si>
+  <si>
+    <t>car-020-1.webp</t>
+  </si>
+  <si>
+    <t>Exact 520i M Sport, G60, white. Korean market. Check angle - the series has 40+ numbered views.</t>
+  </si>
+  <si>
+    <t>BMW G60 520i M Sport Alpine White (5).jpg</t>
+  </si>
+  <si>
+    <t>car-020-2.webp</t>
+  </si>
+  <si>
+    <t>Same car as car-020-1. Check angle.</t>
+  </si>
+  <si>
+    <t>BMW G60 520i M Sport Alpine White (22).jpg</t>
+  </si>
+  <si>
+    <t>car-020-3.webp</t>
+  </si>
+  <si>
+    <t>Same car as car-020-1. Check angle (may be interior).</t>
+  </si>
+  <si>
+    <t>BMW X5 2026</t>
+  </si>
+  <si>
+    <t>BMW G05 LCI X5 xDrive40i M Sport Carbon Black Metallic (1).jpg</t>
+  </si>
+  <si>
+    <t>car-021-1.webp</t>
+  </si>
+  <si>
+    <t>Exact X5 xDrive40i M Sport, G05 LCI, black. Korean market. Check angle - series has 24 numbered views.</t>
+  </si>
+  <si>
+    <t>BMW G05 LCI X5 xDrive40i M Sport Carbon Black Metallic (2).jpg</t>
+  </si>
+  <si>
+    <t>car-021-2.webp</t>
+  </si>
+  <si>
+    <t>Same car as car-021-1. Check angle.</t>
+  </si>
+  <si>
+    <t>BMW G05 LCI X5 xDrive40i M Sport Carbon Black Metallic (3).jpg</t>
+  </si>
+  <si>
+    <t>car-021-3.webp</t>
+  </si>
+  <si>
+    <t>Ford Explorer 2022</t>
+  </si>
+  <si>
+    <t>2020 Ford Explorer XLT in Oxford White, front left.jpg</t>
+  </si>
+  <si>
+    <t>car-022-1.webp</t>
+  </si>
+  <si>
+    <t>2020 XLT, U625 pre-facelift - same as 2022 XLT. Requested color.</t>
+  </si>
+  <si>
+    <t>2020 Ford Explorer XLT in Oxford White, rear left.jpg</t>
+  </si>
+  <si>
+    <t>car-022-2.webp</t>
+  </si>
+  <si>
+    <t>Same car as car-022-1.</t>
+  </si>
+  <si>
+    <t>2022 Ford Explorer interior.jpg</t>
+  </si>
+  <si>
+    <t>car-022-3.webp</t>
+  </si>
+  <si>
+    <t>Dashboard of a 2022 Explorer XLT 4WD - exact model year and trim.</t>
+  </si>
+  <si>
+    <t>Land Rover Defender 2024</t>
+  </si>
+  <si>
+    <t>Land Rover Defender 110 (L663) 1X7A1919.jpg</t>
   </si>
   <si>
     <t>Alexander-93</t>
@@ -920,226 +1454,28 @@
     <t>الصورة: Alexander-93 / Wikimedia Commons — CC BY-SA 4.0</t>
   </si>
   <si>
-    <t>car-009-1.webp</t>
-  </si>
-  <si>
-    <t>NX4 facelift</t>
-  </si>
-  <si>
-    <t>Hyundai Tucson (NX4, SWB) Facelift Sindelfingen 2024 IMG 9232.jpg</t>
-  </si>
-  <si>
-    <t>car-009-2.webp</t>
-  </si>
-  <si>
-    <t>Hyundai Elantra 2023</t>
-  </si>
-  <si>
-    <t>2021 Hyundai Elantra SEL (Canada), front 8.28.21.jpg</t>
-  </si>
-  <si>
-    <t>car-010-1.webp</t>
-  </si>
-  <si>
-    <t>CN7 SEL</t>
-  </si>
-  <si>
-    <t>Nissan Altima 2023</t>
-  </si>
-  <si>
-    <t>2023 Nissan Altima SR.png</t>
-  </si>
-  <si>
-    <t>LukaCali</t>
-  </si>
-  <si>
-    <t>الصورة: LukaCali / Wikimedia Commons — CC BY-SA 4.0</t>
-  </si>
-  <si>
-    <t>car-011-1.webp</t>
-  </si>
-  <si>
-    <t>L34 facelift</t>
-  </si>
-  <si>
-    <t>0 Nissan Altima 0.jpg</t>
-  </si>
-  <si>
-    <t>car-011-2.webp</t>
-  </si>
-  <si>
-    <t>L34</t>
-  </si>
-  <si>
-    <t>Nissan Patrol 2026</t>
-  </si>
-  <si>
-    <t>MIAS 2025 - Nissan Patrol Y63 LE V6T 01.jpg</t>
-  </si>
-  <si>
-    <t>Ethan Llamas</t>
-  </si>
-  <si>
-    <t>الصورة: Ethan Llamas / Wikimedia Commons — CC BY-SA 4.0</t>
-  </si>
-  <si>
-    <t>car-012-1.webp</t>
-  </si>
-  <si>
-    <t>Y63 LE V6T</t>
-  </si>
-  <si>
-    <t>Nissan Patrol V6T LE Titanium.jpg</t>
-  </si>
-  <si>
-    <t>car-012-2.webp</t>
-  </si>
-  <si>
-    <t>Y63 LE Titanium</t>
-  </si>
-  <si>
-    <t>Nissan Patrol Y63 3.5 V6T LE interior.jpg</t>
-  </si>
-  <si>
-    <t>car-012-3.webp</t>
-  </si>
-  <si>
-    <t>Y63 interior</t>
-  </si>
-  <si>
-    <t>Chevrolet Malibu 2023</t>
-  </si>
-  <si>
-    <t>0 Chevrolet Malibu (E2XX) 10.jpg</t>
-  </si>
-  <si>
-    <t>car-014-1.webp</t>
-  </si>
-  <si>
-    <t>E2XX (2016+)</t>
-  </si>
-  <si>
-    <t>2023 Chevrolet Malibu RS Auto.jpg</t>
-  </si>
-  <si>
-    <t>Calreyn88 (verify on file page)</t>
-  </si>
-  <si>
-    <t>الصورة: Calreyn88 (verify on file page) / Wikimedia Commons — CC BY-SA 4.0</t>
-  </si>
-  <si>
-    <t>car-014-2.webp</t>
-  </si>
-  <si>
-    <t>2023 RS</t>
-  </si>
-  <si>
-    <t>Chevrolet Tahoe 2023</t>
-  </si>
-  <si>
-    <t>2021 Chevrolet Tahoe front view (United States).jpg</t>
-  </si>
-  <si>
-    <t>Gold Pony</t>
-  </si>
-  <si>
-    <t>الصورة: Gold Pony / Wikimedia Commons — CC BY-SA 4.0</t>
-  </si>
-  <si>
-    <t>car-015-1.webp</t>
-  </si>
-  <si>
-    <t>T1XX</t>
-  </si>
-  <si>
-    <t>Production 2021 Chevrolet Tahoe Z71 in wild.jpg</t>
-  </si>
-  <si>
-    <t>Unknown0124</t>
-  </si>
-  <si>
-    <t>الصورة: Unknown0124 / Wikimedia Commons — CC BY-SA 4.0</t>
-  </si>
-  <si>
-    <t>car-015-2.webp</t>
-  </si>
-  <si>
-    <t>T1XX Z71</t>
-  </si>
-  <si>
-    <t>2022 Lexus ES 350 (GSZ10) 1X7A0296.jpg</t>
-  </si>
-  <si>
-    <t>Alexander Migl</t>
-  </si>
-  <si>
-    <t>الصورة: Alexander Migl / Wikimedia Commons — CC BY-SA 4.0</t>
-  </si>
-  <si>
-    <t>car-016-1.webp</t>
-  </si>
-  <si>
-    <t>ES facelift</t>
-  </si>
-  <si>
-    <t>2022 Lexus ES 350 (GSZ10) 1X7A5794.jpg</t>
-  </si>
-  <si>
-    <t>car-016-2.webp</t>
-  </si>
-  <si>
-    <t>2023 Lexus RX 350 (front).jpg</t>
-  </si>
-  <si>
-    <t>Carlito714</t>
-  </si>
-  <si>
-    <t>الصورة: Carlito714 / Wikimedia Commons — CC BY-SA 4.0</t>
-  </si>
-  <si>
-    <t>car-017-1.webp</t>
-  </si>
-  <si>
-    <t>AL30</t>
-  </si>
-  <si>
-    <t>2023 Lexus RX 350 (rear).jpg</t>
-  </si>
-  <si>
-    <t>car-017-2.webp</t>
-  </si>
-  <si>
-    <t>AL30, rear</t>
-  </si>
-  <si>
-    <t>Mercedes C 300 2024</t>
-  </si>
-  <si>
-    <t>Mercedes-Benz W206 C 300 4MATIC AMG Line Polar White (14).jpg</t>
-  </si>
-  <si>
-    <t>Damian B Oh</t>
-  </si>
-  <si>
-    <t>الصورة: Damian B Oh / Wikimedia Commons — CC BY-SA 4.0</t>
-  </si>
-  <si>
-    <t>car-018-1.webp</t>
-  </si>
-  <si>
-    <t>W206 AMG Line, white</t>
-  </si>
-  <si>
-    <t>Mercedes-Benz W206 C 300 4MATIC AMG Line Polar White (23).jpg</t>
-  </si>
-  <si>
-    <t>car-018-2.webp</t>
-  </si>
-  <si>
-    <t>Mercedes GLE 450 2026</t>
-  </si>
-  <si>
-    <t>Mercedes-Benz GLE 450 d 4MATIC Sports Edition Black Stars (W167) front.jpg</t>
+    <t>car-023-1.webp</t>
+  </si>
+  <si>
+    <t>L663 110 body. Trim not stated. Check angle/color; no white X-Dynamic SE found.</t>
+  </si>
+  <si>
+    <t>Land Rover Defender 110 First Edition 2020 - rear.jpg</t>
+  </si>
+  <si>
+    <t>DeFacto</t>
+  </si>
+  <si>
+    <t>الصورة: DeFacto / Wikimedia Commons — CC BY-SA 4.0</t>
+  </si>
+  <si>
+    <t>car-023-2.webp</t>
+  </si>
+  <si>
+    <t>2020 Defender 110 First Edition (L663) - same body as 2024 110.</t>
+  </si>
+  <si>
+    <t>Land Rover DEFENDER 110 S ADVENTURE PACK (3BA-LE72XAA) interior.jpg</t>
   </si>
   <si>
     <t>Tokumeigakarinoaoshima</t>
@@ -1148,148 +1484,10 @@
     <t>الصورة: Tokumeigakarinoaoshima / Wikimedia Commons — CC BY-SA 4.0</t>
   </si>
   <si>
-    <t>car-019-1.webp</t>
-  </si>
-  <si>
-    <t>V167 facelift (Japan), black</t>
-  </si>
-  <si>
-    <t>Mercedes-Benz GLE 450 d 4MATIC Sports Edition Black Stars (W167) rear.jpg</t>
-  </si>
-  <si>
-    <t>car-019-2.webp</t>
-  </si>
-  <si>
-    <t>V167 facelift, rear</t>
-  </si>
-  <si>
-    <t>2020 Nissan Versa SV 1.6L, front 2.29.20.jpg</t>
-  </si>
-  <si>
-    <t>car-013-1.webp</t>
-  </si>
-  <si>
-    <t>N18 (GCC Sunny = Versa N18)</t>
-  </si>
-  <si>
-    <t>2020 Nissan Versa SR front NYIAS 2019.jpg</t>
-  </si>
-  <si>
-    <t>car-013-2.webp</t>
-  </si>
-  <si>
-    <t>N18 show car</t>
-  </si>
-  <si>
-    <t>BMW 520i 2026</t>
-  </si>
-  <si>
-    <t>BMW G60 520i M Sport Alpine White (45).jpg</t>
-  </si>
-  <si>
-    <t>car-020-1.webp</t>
-  </si>
-  <si>
-    <t>G60 520i M Sport, white</t>
-  </si>
-  <si>
-    <t>BMW G60 520i 1X7A2446.jpg</t>
-  </si>
-  <si>
-    <t>car-020-2.webp</t>
-  </si>
-  <si>
-    <t>G60 520i</t>
-  </si>
-  <si>
-    <t>BMW X5 2026</t>
-  </si>
-  <si>
-    <t>BMW G05 LCI X5 xDrive40i M Sport Carbon Black Metallic (22).jpg</t>
-  </si>
-  <si>
-    <t>car-021-1.webp</t>
-  </si>
-  <si>
-    <t>G05 LCI xDrive40i, black</t>
-  </si>
-  <si>
-    <t>BMW G05 LCI X5 xDrive40i M Sport Carbon Black Metallic (3).jpg</t>
-  </si>
-  <si>
-    <t>car-021-2.webp</t>
-  </si>
-  <si>
-    <t>2024 BMW X5 (G05 LCI).jpg</t>
-  </si>
-  <si>
-    <t>Oleg Yunakov</t>
-  </si>
-  <si>
-    <t>الصورة: Oleg Yunakov / Wikimedia Commons — CC BY-SA 4.0</t>
-  </si>
-  <si>
-    <t>car-021-3.webp</t>
-  </si>
-  <si>
-    <t>G05 LCI</t>
-  </si>
-  <si>
-    <t>Ford Explorer 2022</t>
-  </si>
-  <si>
-    <t>2020 Ford Explorer XLT in Oxford White, front left.jpg</t>
-  </si>
-  <si>
-    <t>Mr.choppers</t>
-  </si>
-  <si>
-    <t>CC BY-SA 3.0</t>
-  </si>
-  <si>
-    <t>الصورة: Mr.choppers / Wikimedia Commons — CC BY-SA 3.0</t>
-  </si>
-  <si>
-    <t>car-022-1.webp</t>
-  </si>
-  <si>
-    <t>U625 XLT, white</t>
-  </si>
-  <si>
-    <t>2020 Ford Explorer XLT, rear 2.29.20.jpg</t>
-  </si>
-  <si>
-    <t>car-022-2.webp</t>
-  </si>
-  <si>
-    <t>U625 XLT, rear</t>
-  </si>
-  <si>
-    <t>Land Rover Defender 2024</t>
-  </si>
-  <si>
-    <t>Land Rover Defender (L663) Auto Zuerich 2021 IMG 0432.jpg</t>
-  </si>
-  <si>
-    <t>car-023-1.webp</t>
-  </si>
-  <si>
-    <t>L663</t>
-  </si>
-  <si>
-    <t>Land Rover Defender 110 First Edition 2020 - rear.jpg</t>
-  </si>
-  <si>
-    <t>DeFacto</t>
-  </si>
-  <si>
-    <t>الصورة: DeFacto / Wikimedia Commons — CC BY-SA 4.0</t>
-  </si>
-  <si>
-    <t>car-023-2.webp</t>
-  </si>
-  <si>
-    <t>L663 110, rear</t>
+    <t>car-023-3.webp</t>
+  </si>
+  <si>
+    <t>Japanese-market 110 S interior (right-hand drive - GCC cars are left-hand drive).</t>
   </si>
   <si>
     <t>2024 Kia Picanto (JA) Rutesheimer Autoschau 2025 DSC 9198.jpg</t>
@@ -1298,7 +1496,7 @@
     <t>car-024-1.webp</t>
   </si>
   <si>
-    <t>JA facelift</t>
+    <t>2024 Picanto JA (2024 facelift), European market. Check angle/color.</t>
   </si>
   <si>
     <t>2024 Kia Picanto (JA) Rutesheimer Autoschau 2025 DSC 9200.jpg</t>
@@ -1307,61 +1505,82 @@
     <t>car-024-2.webp</t>
   </si>
   <si>
+    <t>Same car/event as car-024-1. Check angle.</t>
+  </si>
+  <si>
+    <t>2024 Kia Picanto (JA) IAA 2025 DSC 1272.jpg</t>
+  </si>
+  <si>
+    <t>car-024-3.webp</t>
+  </si>
+  <si>
+    <t>2024 Picanto JA facelift at IAA 2025 (motor show stand - check background for signage).</t>
+  </si>
+  <si>
     <t>Kia EV6 2026</t>
   </si>
   <si>
+    <t>Kia EV6 GT-line (Facelift) – f 27072025.jpg</t>
+  </si>
+  <si>
+    <t>car-025-1.webp</t>
+  </si>
+  <si>
+    <t>EV6 GT-Line facelift (2025+), European market.</t>
+  </si>
+  <si>
+    <t>Kia EV6 GT-line (Facelift) – h 27072025.jpg</t>
+  </si>
+  <si>
+    <t>car-025-2.webp</t>
+  </si>
+  <si>
+    <t>Same car as car-025-1.</t>
+  </si>
+  <si>
     <t>2025 Kia EV6 GT-Line Auto Zuerich 2024 DSC 6468.jpg</t>
   </si>
   <si>
-    <t>car-025-1.webp</t>
-  </si>
-  <si>
-    <t>EV6 facelift GT-Line</t>
-  </si>
-  <si>
-    <t>Kia EV6 GT-line (Facelift) – f 27072025.jpg</t>
-  </si>
-  <si>
-    <t>M 93</t>
-  </si>
-  <si>
-    <t>CC BY-SA 3.0 de</t>
-  </si>
-  <si>
-    <t>الصورة: M 93 / Wikimedia Commons — CC BY-SA 3.0 de</t>
-  </si>
-  <si>
-    <t>car-025-2.webp</t>
+    <t>car-025-3.webp</t>
+  </si>
+  <si>
+    <t>EV6 GT-Line facelift at Auto Zürich 2024 (motor show - check background).</t>
   </si>
   <si>
     <t>Toyota Camry 2026</t>
   </si>
   <si>
-    <t>2025 Toyota Camry Hybrid SE Upgrade AWD in Midnight Black Metallic, front right, 2024-11-06.jpg</t>
+    <t>Toyota Camry E in Emotional Red 01.jpg</t>
+  </si>
+  <si>
+    <t>Haysnawri10</t>
+  </si>
+  <si>
+    <t>الصورة: Haysnawri10 / Wikimedia Commons — CC BY-SA 4.0</t>
   </si>
   <si>
     <t>car-026-1.webp</t>
   </si>
   <si>
-    <t>XV80 SE Hybrid, black</t>
-  </si>
-  <si>
-    <t>2025 Toyota Camry Hybrid SE Upgrade AWD in Midnight Black Metallic, rear right, 2024-11-06.jpg</t>
+    <t>XV80 photographed in Makkah, Saudi Arabia (GCC market). Base 'E' trim - SE has a sportier bumper/grille. Color differs from requested black. Check angle.</t>
+  </si>
+  <si>
+    <t>Toyota Camry E in Emotional Red 02.jpg</t>
   </si>
   <si>
     <t>car-026-2.webp</t>
   </si>
   <si>
-    <t>XV80 SE Hybrid, rear</t>
-  </si>
-  <si>
-    <t>25 Toyota Camry XSE.jpg</t>
+    <t>Same car as car-026-1.</t>
+  </si>
+  <si>
+    <t>25 Toyota Camry LE.jpg</t>
   </si>
   <si>
     <t>car-026-3.webp</t>
   </si>
   <si>
-    <t>XV80 XSE</t>
+    <t>2025 US Camry LE (XV80, hybrid-only generation). LE front differs from SE. Shot on a dealer lot by a Commons user.</t>
   </si>
   <si>
     <t>Honda Civic 2023</t>
@@ -1379,43 +1598,70 @@
     <t>car-027-1.webp</t>
   </si>
   <si>
-    <t>11th gen Sport sedan</t>
-  </si>
-  <si>
-    <t>2022 Honda Civic Sport, Rear Right, 06-20-2021.jpg</t>
+    <t>11th gen sedan, Sport trim, North American. 2022 = same pre-refresh body as 2023.</t>
+  </si>
+  <si>
+    <t>Honda Civic (2021) sedan Sport DSC 7057.jpg</t>
   </si>
   <si>
     <t>car-027-2.webp</t>
   </si>
   <si>
-    <t>11th gen Sport, rear</t>
-  </si>
-  <si>
-    <t>Mitsubishi Pajero IV LWB facelift 01 China 2015-04-13.jpg</t>
-  </si>
-  <si>
-    <t>Navigator84</t>
-  </si>
-  <si>
-    <t>الصورة: Navigator84 / Wikimedia Commons — CC BY-SA 4.0</t>
+    <t>11th gen sedan Sport. Check angle/color.</t>
+  </si>
+  <si>
+    <t>Honda Civic (2021) sedan Sport DSC 7054.jpg</t>
+  </si>
+  <si>
+    <t>car-027-3.webp</t>
+  </si>
+  <si>
+    <t>Same car as car-027-2. Check angle.</t>
+  </si>
+  <si>
+    <t>Mitsubishi Pajero CN Spec V6 3.0L(After Second Facelift)01.jpg</t>
+  </si>
+  <si>
+    <t>Tangjunwen CN</t>
+  </si>
+  <si>
+    <t>الصورة: Tangjunwen CN / Wikimedia Commons — CC BY-SA 4.0</t>
   </si>
   <si>
     <t>car-028-1.webp</t>
   </si>
   <si>
-    <t>V90 LWB facelift</t>
-  </si>
-  <si>
-    <t>Mitsubishi Pajero IV LWB facelift 2 China 2015-04-23.jpg</t>
+    <t>4th gen Pajero after its second (final) facelift, Chinese-spec 3.0 V6. Confirm it is the long-wheelbase 5-door body. Check angle/color.</t>
+  </si>
+  <si>
+    <t>Mitsubishi Pajero CN Spec V6 3.0L(After Second Facelift)02.jpg</t>
   </si>
   <si>
     <t>car-028-2.webp</t>
   </si>
   <si>
+    <t>Same car as car-028-1.</t>
+  </si>
+  <si>
+    <t>2019 pajero final edition interior.jpg</t>
+  </si>
+  <si>
+    <t>マッドキラー</t>
+  </si>
+  <si>
+    <t>الصورة: マッドキラー / Wikimedia Commons — CC BY-SA 4.0</t>
+  </si>
+  <si>
+    <t>car-028-3.webp</t>
+  </si>
+  <si>
+    <t>2019 Japanese Pajero Final Edition interior (right-hand drive - GCC cars are left-hand drive).</t>
+  </si>
+  <si>
     <t>Toyota Hilux 2024</t>
   </si>
   <si>
-    <t>2021 Toyota Hilux Revo GR Sport Double-Cab 2.8 4x4.jpg</t>
+    <t>2024 Toyota Hilux Revo Z-Edition Double-Cab 2.4 Mid.jpg</t>
   </si>
   <si>
     <t>Chanokchon</t>
@@ -1427,130 +1673,169 @@
     <t>car-029-1.webp</t>
   </si>
   <si>
-    <t>AN120 facelift double cab</t>
-  </si>
-  <si>
-    <t>Toyota Hilux Double Cab 2.4 AWD (2021) (52180166719).jpg</t>
-  </si>
-  <si>
-    <t>Charles (Flickr)</t>
-  </si>
-  <si>
-    <t>CC BY 2.0</t>
-  </si>
-  <si>
-    <t>الصورة: Charles (Flickr) / Wikimedia Commons — CC BY 2.0</t>
+    <t>8th gen 2020+ facelift double cab (Thai Revo Z-Edition). Front bumper/grille differ from GCC 2.7 base trims. Photographed at a Toyota showroom by a Commons user.</t>
+  </si>
+  <si>
+    <t>Toyota Hilux 4x2 G 2022.jpg</t>
+  </si>
+  <si>
+    <t>Captainmorlypogi1959</t>
+  </si>
+  <si>
+    <t>الصورة: Captainmorlypogi1959 / Wikimedia Commons — CC BY-SA 4.0</t>
   </si>
   <si>
     <t>car-029-2.webp</t>
   </si>
   <si>
-    <t>AN120 double cab</t>
+    <t>Philippine 2022 Hilux G double cab, 2020+ facelift. Check angle/color.</t>
+  </si>
+  <si>
+    <t>Toyota Hilux 4x2 G 2024 (2).jpg</t>
+  </si>
+  <si>
+    <t>car-029-3.webp</t>
+  </si>
+  <si>
+    <t>Philippine 2024 Hilux G (street shot). Check angle and that the whole car is in frame.</t>
+  </si>
+  <si>
+    <t>Changan CS75 Plus III 001.jpg</t>
+  </si>
+  <si>
+    <t>JustAnotherCarDesigner</t>
+  </si>
+  <si>
+    <t>JustAnotherCarDesigner / Wikimedia Commons (CC0)</t>
+  </si>
+  <si>
+    <t>car-030-1.webp</t>
+  </si>
+  <si>
+    <t>3rd gen CS75 Plus (stated in title), China. Note: the same uploader has a separate 2026 facelift set; confirm which face the Middle East 2026 car uses.</t>
   </si>
   <si>
     <t>Changan CS75 Plus III 002.jpg</t>
   </si>
   <si>
-    <t>JustAnotherCarDesigner</t>
-  </si>
-  <si>
-    <t>JustAnotherCarDesigner / Wikimedia Commons (CC0)</t>
-  </si>
-  <si>
-    <t>car-030-1.webp</t>
-  </si>
-  <si>
-    <t>3rd gen (2024+)</t>
-  </si>
-  <si>
-    <t>Moscow - 2026 - Geely Coolray compact crossover.jpg</t>
-  </si>
-  <si>
-    <t>Юрий Д.К.</t>
-  </si>
-  <si>
-    <t>CC BY 4.0</t>
-  </si>
-  <si>
-    <t>الصورة: Юрий Д.К. / Wikimedia Commons — CC BY 4.0</t>
+    <t>car-030-2.webp</t>
+  </si>
+  <si>
+    <t>Same series as car-030-1.</t>
+  </si>
+  <si>
+    <t>Moscow, Changan CS75 plus grey, May 2026 02.jpg</t>
+  </si>
+  <si>
+    <t>car-030-3.webp</t>
+  </si>
+  <si>
+    <t>Requested color. Generation NOT stated in metadata - street photo in Moscow 2026; confirm it is the 3rd gen before use.</t>
+  </si>
+  <si>
+    <t>Geely Binyue Cool 001.jpg</t>
+  </si>
+  <si>
+    <t>الصورة: JustAnotherCarDesigner / Wikimedia Commons — CC BY-SA 4.0</t>
   </si>
   <si>
     <t>car-031-1.webp</t>
   </si>
   <si>
-    <t>2026 Coolray</t>
-  </si>
-  <si>
-    <t>Haval H6 III 007.jpg</t>
-  </si>
-  <si>
-    <t>Jengtingchen</t>
-  </si>
-  <si>
-    <t>الصورة: Jengtingchen / Wikimedia Commons — CC BY-SA 4.0</t>
+    <t>Geely Binyue Cool (China), the newest Binyue/Coolray body. Whether the Middle East 2026 'New Coolray' is exactly this body is NOT confirmed - compare front lamps and full-width tail lamp.</t>
+  </si>
+  <si>
+    <t>Geely Binyue Cool 002.jpg</t>
+  </si>
+  <si>
+    <t>car-031-2.webp</t>
+  </si>
+  <si>
+    <t>Same series as car-031-1.</t>
+  </si>
+  <si>
+    <t>Geely Binyue Cool 003.jpg</t>
+  </si>
+  <si>
+    <t>car-031-3.webp</t>
+  </si>
+  <si>
+    <t>Haval H6 III facelift 002.jpg</t>
   </si>
   <si>
     <t>car-032-1.webp</t>
   </si>
   <si>
-    <t>3rd gen</t>
-  </si>
-  <si>
-    <t>Haval H6 III 010.jpg</t>
+    <t>3rd gen H6 facelift (stated in title), China. Confirm it matches the Middle East 2026 H6 face.</t>
+  </si>
+  <si>
+    <t>Haval H6 III facelift 001.jpg</t>
   </si>
   <si>
     <t>car-032-2.webp</t>
   </si>
   <si>
-    <t>2024 Hyundai Santa Fe (MX5) IMG 5295.jpg</t>
+    <t>Same series as car-032-1.</t>
+  </si>
+  <si>
+    <t>2024 Hyundai Santa Fe Calligraphy AWD in Rockwood Green Pearl, front right.jpg</t>
   </si>
   <si>
     <t>car-033-1.webp</t>
   </si>
   <si>
-    <t>MX5</t>
-  </si>
-  <si>
-    <t>Hyundai Santa Fe, Auto 2024, Zurich (PANA1001).jpg</t>
-  </si>
-  <si>
-    <t>Matti Blume</t>
-  </si>
-  <si>
-    <t>الصورة: Matti Blume / Wikimedia Commons — CC BY-SA 4.0</t>
+    <t>MX5, US Calligraphy AWD (2.5T engine in US). Requested color.</t>
+  </si>
+  <si>
+    <t>2024 Hyundai Santa Fe Calligraphy AWD in Rockwood Green Pearl, rear right.jpg</t>
   </si>
   <si>
     <t>car-033-2.webp</t>
   </si>
   <si>
-    <t>2023 Chery Tiggo8 Pro Max (LVТ) silver front.jpg</t>
-  </si>
-  <si>
-    <t>Throwawayacc222</t>
-  </si>
-  <si>
-    <t>Throwawayacc222 / Wikimedia Commons (CC0)</t>
+    <t>Same car as car-033-1.</t>
+  </si>
+  <si>
+    <t>Hyundai Santa Fe MX5 2.5T Calligraphy HTRAC Ocado Green Pearl.jpg</t>
+  </si>
+  <si>
+    <t>car-033-3.webp</t>
+  </si>
+  <si>
+    <t>MX5 2.5T Calligraphy HTRAC in green (Philippine market). Check angle.</t>
+  </si>
+  <si>
+    <t>2024 Chery Tiggo 8 Pro Max in Bandung, Jawa Barat 40266 01.jpg</t>
+  </si>
+  <si>
+    <t>MoCars</t>
+  </si>
+  <si>
+    <t>MoCars / Wikimedia Commons (CC0)</t>
   </si>
   <si>
     <t>car-034-1.webp</t>
   </si>
   <si>
-    <t>silver (title has Cyrillic Т)</t>
-  </si>
-  <si>
-    <t>Chirey Tiggo 8 Pro Max.jpg</t>
-  </si>
-  <si>
-    <t>DestinationFearFan</t>
-  </si>
-  <si>
-    <t>الصورة: DestinationFearFan / Wikimedia Commons — CC BY 4.0</t>
+    <t>Tiggo 8 Pro Max (Indonesia). Whether this is the 2025-2026 latest facelift is not stated - compare grille/lamps with the current Middle East car. Color differs from silver.</t>
+  </si>
+  <si>
+    <t>Chirey Tiggo 8 Pro Max - Rear.jpeg</t>
+  </si>
+  <si>
+    <t>Bull-Doser</t>
+  </si>
+  <si>
+    <t>Public domain</t>
+  </si>
+  <si>
+    <t>Bull-Doser / Wikimedia Commons (Public domain)</t>
   </si>
   <si>
     <t>car-034-2.webp</t>
   </si>
   <si>
-    <t>Mexico (Chirey)</t>
+    <t>Mexican-market Tiggo 8 Pro Max (sold as Chirey). Facelift status not stated. Just above the 1600 px minimum.</t>
   </si>
   <si>
     <t>الماركة / الجهة</t>
@@ -3995,7 +4280,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J71"/>
+  <dimension ref="A1:J99"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -4084,57 +4369,57 @@
         <v>205</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>199</v>
       </c>
       <c r="F3" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="H3" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="J3" s="7" t="s">
         <v>207</v>
-      </c>
-      <c r="G3" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="H3" s="11" t="s">
-        <v>202</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>208</v>
-      </c>
-      <c r="J3" s="7" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B4" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="E4" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="F4" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="G4" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="H4" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="I4" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="J4" s="7" t="s">
         <v>213</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="G4" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="H4" s="11" t="s">
-        <v>202</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>215</v>
-      </c>
-      <c r="J4" s="7" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -4142,19 +4427,19 @@
         <v>44</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="C5" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="E5" s="6" t="s">
         <v>217</v>
       </c>
-      <c r="D5" s="6" t="s">
-        <v>212</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>213</v>
-      </c>
       <c r="F5" s="7" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="G5" s="11" t="s">
         <v>201</v>
@@ -4163,30 +4448,30 @@
         <v>202</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>199</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="G6" s="11" t="s">
         <v>201</v>
@@ -4195,42 +4480,42 @@
         <v>202</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>226</v>
+        <v>209</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="F7" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="G7" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="H7" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="I7" s="6" t="s">
         <v>227</v>
       </c>
-      <c r="G7" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="H7" s="11" t="s">
-        <v>202</v>
-      </c>
-      <c r="I7" s="6" t="s">
+      <c r="J7" s="7" t="s">
         <v>228</v>
-      </c>
-      <c r="J7" s="7" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -4238,19 +4523,19 @@
         <v>48</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>230</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="G8" s="11" t="s">
         <v>201</v>
@@ -4259,30 +4544,30 @@
         <v>202</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="G9" s="11" t="s">
         <v>201</v>
@@ -4291,30 +4576,30 @@
         <v>202</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>199</v>
+        <v>237</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G10" s="11" t="s">
         <v>201</v>
@@ -4323,30 +4608,30 @@
         <v>202</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>198</v>
+        <v>248</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>199</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>200</v>
+        <v>249</v>
       </c>
       <c r="G11" s="11" t="s">
         <v>201</v>
@@ -4355,30 +4640,30 @@
         <v>202</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>199</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="G12" s="11" t="s">
         <v>201</v>
@@ -4387,30 +4672,30 @@
         <v>202</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="E13" s="6" t="s">
         <v>199</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="G13" s="11" t="s">
         <v>201</v>
@@ -4419,30 +4704,30 @@
         <v>202</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>199</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="G14" s="11" t="s">
         <v>201</v>
@@ -4451,30 +4736,30 @@
         <v>202</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>70</v>
+        <v>260</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E15" s="6" t="s">
         <v>199</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="G15" s="11" t="s">
         <v>201</v>
@@ -4483,30 +4768,30 @@
         <v>202</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>70</v>
+        <v>260</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>199</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="G16" s="11" t="s">
         <v>201</v>
@@ -4515,30 +4800,30 @@
         <v>202</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>75</v>
+        <v>272</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>269</v>
+        <v>198</v>
       </c>
       <c r="E17" s="6" t="s">
         <v>199</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>270</v>
+        <v>200</v>
       </c>
       <c r="G17" s="11" t="s">
         <v>201</v>
@@ -4547,30 +4832,30 @@
         <v>202</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>75</v>
+        <v>272</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="G18" s="11" t="s">
         <v>201</v>
@@ -4579,30 +4864,30 @@
         <v>202</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>75</v>
+        <v>272</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="G19" s="11" t="s">
         <v>201</v>
@@ -4611,30 +4896,30 @@
         <v>202</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>199</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="G20" s="11" t="s">
         <v>201</v>
@@ -4643,30 +4928,30 @@
         <v>202</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="E21" s="6" t="s">
         <v>199</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="G21" s="11" t="s">
         <v>201</v>
@@ -4675,30 +4960,30 @@
         <v>202</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>286</v>
+        <v>70</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>261</v>
+        <v>198</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>199</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>262</v>
+        <v>200</v>
       </c>
       <c r="G22" s="11" t="s">
         <v>201</v>
@@ -4707,30 +4992,30 @@
         <v>202</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="J22" s="7" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>290</v>
+        <v>75</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="E23" s="6" t="s">
         <v>199</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="G23" s="11" t="s">
         <v>201</v>
@@ -4739,30 +5024,30 @@
         <v>202</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="J23" s="7" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>290</v>
+        <v>75</v>
       </c>
       <c r="C24" s="7" t="s">
+        <v>300</v>
+      </c>
+      <c r="D24" s="6" t="s">
         <v>296</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>206</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>199</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>207</v>
+        <v>297</v>
       </c>
       <c r="G24" s="11" t="s">
         <v>201</v>
@@ -4771,30 +5056,30 @@
         <v>202</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="J24" s="7" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>299</v>
+        <v>75</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>301</v>
+        <v>209</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>302</v>
+        <v>211</v>
       </c>
       <c r="G25" s="11" t="s">
         <v>201</v>
@@ -4803,30 +5088,30 @@
         <v>202</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="J25" s="7" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>299</v>
+        <v>78</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>226</v>
+        <v>307</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>213</v>
+        <v>199</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>227</v>
+        <v>308</v>
       </c>
       <c r="G26" s="11" t="s">
         <v>201</v>
@@ -4835,30 +5120,30 @@
         <v>202</v>
       </c>
       <c r="I26" s="6" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="J26" s="7" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>299</v>
+        <v>78</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="E27" s="6" t="s">
         <v>199</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="G27" s="11" t="s">
         <v>201</v>
@@ -4867,30 +5152,30 @@
         <v>202</v>
       </c>
       <c r="I27" s="6" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="J27" s="7" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>311</v>
+        <v>78</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>206</v>
+        <v>307</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>199</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>207</v>
+        <v>308</v>
       </c>
       <c r="G28" s="11" t="s">
         <v>201</v>
@@ -4899,30 +5184,30 @@
         <v>202</v>
       </c>
       <c r="I28" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="J28" s="7" t="s">
         <v>313</v>
-      </c>
-      <c r="J28" s="7" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="E29" s="6" t="s">
         <v>199</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="G29" s="11" t="s">
         <v>201</v>
@@ -4931,50 +5216,50 @@
         <v>202</v>
       </c>
       <c r="I29" s="6" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="J29" s="7" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>199</v>
       </c>
       <c r="F30" s="7" t="s">
+        <v>319</v>
+      </c>
+      <c r="G30" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="H30" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="I30" s="6" t="s">
         <v>323</v>
       </c>
-      <c r="G30" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="H30" s="11" t="s">
-        <v>202</v>
-      </c>
-      <c r="I30" s="6" t="s">
+      <c r="J30" s="7" t="s">
         <v>324</v>
-      </c>
-      <c r="J30" s="7" t="s">
-        <v>325</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="C31" s="7" t="s">
         <v>326</v>
@@ -5003,54 +5288,54 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>107</v>
+        <v>325</v>
       </c>
       <c r="C32" s="7" t="s">
         <v>331</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>199</v>
       </c>
       <c r="F32" s="7" t="s">
+        <v>328</v>
+      </c>
+      <c r="G32" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="H32" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="I32" s="6" t="s">
+        <v>332</v>
+      </c>
+      <c r="J32" s="7" t="s">
         <v>333</v>
-      </c>
-      <c r="G32" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="H32" s="11" t="s">
-        <v>202</v>
-      </c>
-      <c r="I32" s="6" t="s">
-        <v>334</v>
-      </c>
-      <c r="J32" s="7" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>107</v>
+        <v>325</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="E33" s="6" t="s">
         <v>199</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="G33" s="11" t="s">
         <v>201</v>
@@ -5062,27 +5347,27 @@
         <v>337</v>
       </c>
       <c r="J33" s="7" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>111</v>
+        <v>339</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="G34" s="11" t="s">
         <v>201</v>
@@ -5091,30 +5376,30 @@
         <v>202</v>
       </c>
       <c r="I34" s="6" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="J34" s="7" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="6" t="s">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>111</v>
+        <v>339</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>339</v>
+        <v>248</v>
       </c>
       <c r="E35" s="6" t="s">
         <v>199</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>340</v>
+        <v>249</v>
       </c>
       <c r="G35" s="11" t="s">
         <v>201</v>
@@ -5123,62 +5408,62 @@
         <v>202</v>
       </c>
       <c r="I35" s="6" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="J35" s="7" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
-        <v>115</v>
+        <v>88</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>348</v>
+        <v>248</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>199</v>
       </c>
       <c r="F36" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="G36" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="H36" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="I36" s="6" t="s">
         <v>349</v>
       </c>
-      <c r="G36" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="H36" s="11" t="s">
-        <v>202</v>
-      </c>
-      <c r="I36" s="6" t="s">
+      <c r="J36" s="7" t="s">
         <v>350</v>
-      </c>
-      <c r="J36" s="7" t="s">
-        <v>351</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="6" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>346</v>
+        <v>94</v>
       </c>
       <c r="C37" s="7" t="s">
+        <v>351</v>
+      </c>
+      <c r="D37" s="6" t="s">
         <v>352</v>
       </c>
-      <c r="D37" s="6" t="s">
-        <v>348</v>
-      </c>
       <c r="E37" s="6" t="s">
-        <v>199</v>
+        <v>353</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="G37" s="11" t="s">
         <v>201</v>
@@ -5187,30 +5472,30 @@
         <v>202</v>
       </c>
       <c r="I37" s="6" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="J37" s="7" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
-        <v>119</v>
+        <v>93</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>354</v>
+        <v>94</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>356</v>
+        <v>209</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>357</v>
+        <v>211</v>
       </c>
       <c r="G38" s="11" t="s">
         <v>201</v>
@@ -5227,22 +5512,22 @@
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
-        <v>119</v>
+        <v>93</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>354</v>
+        <v>94</v>
       </c>
       <c r="C39" s="7" t="s">
         <v>360</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="E39" s="6" t="s">
         <v>199</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="G39" s="11" t="s">
         <v>201</v>
@@ -5251,30 +5536,30 @@
         <v>202</v>
       </c>
       <c r="I39" s="6" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="J39" s="7" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="6" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>94</v>
+        <v>365</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>261</v>
+        <v>198</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>199</v>
       </c>
       <c r="F40" s="7" t="s">
-        <v>262</v>
+        <v>200</v>
       </c>
       <c r="G40" s="11" t="s">
         <v>201</v>
@@ -5283,30 +5568,30 @@
         <v>202</v>
       </c>
       <c r="I40" s="6" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="J40" s="7" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="6" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>94</v>
+        <v>365</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>261</v>
+        <v>198</v>
       </c>
       <c r="E41" s="6" t="s">
         <v>199</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>262</v>
+        <v>200</v>
       </c>
       <c r="G41" s="11" t="s">
         <v>201</v>
@@ -5315,30 +5600,30 @@
         <v>202</v>
       </c>
       <c r="I41" s="6" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="J41" s="7" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="6" t="s">
-        <v>124</v>
+        <v>102</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>348</v>
+        <v>285</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>199</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>349</v>
+        <v>286</v>
       </c>
       <c r="G42" s="11" t="s">
         <v>201</v>
@@ -5347,30 +5632,30 @@
         <v>202</v>
       </c>
       <c r="I42" s="6" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="J42" s="7" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="6" t="s">
-        <v>124</v>
+        <v>102</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="E43" s="6" t="s">
         <v>199</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="G43" s="11" t="s">
         <v>201</v>
@@ -5379,30 +5664,30 @@
         <v>202</v>
       </c>
       <c r="I43" s="6" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="J43" s="7" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="6" t="s">
-        <v>128</v>
+        <v>102</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>348</v>
+        <v>248</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>199</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>349</v>
+        <v>249</v>
       </c>
       <c r="G44" s="11" t="s">
         <v>201</v>
@@ -5411,30 +5696,30 @@
         <v>202</v>
       </c>
       <c r="I44" s="6" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="J44" s="7" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="6" t="s">
-        <v>128</v>
+        <v>106</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>376</v>
+        <v>107</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>348</v>
+        <v>383</v>
       </c>
       <c r="E45" s="6" t="s">
         <v>199</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>349</v>
+        <v>384</v>
       </c>
       <c r="G45" s="11" t="s">
         <v>201</v>
@@ -5443,30 +5728,30 @@
         <v>202</v>
       </c>
       <c r="I45" s="6" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="J45" s="7" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
-        <v>128</v>
+        <v>106</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>376</v>
+        <v>107</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="G46" s="11" t="s">
         <v>201</v>
@@ -5475,30 +5760,30 @@
         <v>202</v>
       </c>
       <c r="I46" s="6" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="J46" s="7" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="6" t="s">
-        <v>132</v>
+        <v>106</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>387</v>
+        <v>107</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>390</v>
+        <v>199</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
       <c r="G47" s="11" t="s">
         <v>201</v>
@@ -5507,30 +5792,30 @@
         <v>202</v>
       </c>
       <c r="I47" s="6" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="J47" s="7" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
-        <v>132</v>
+        <v>110</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>387</v>
+        <v>111</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>261</v>
+        <v>216</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>199</v>
+        <v>217</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>262</v>
+        <v>218</v>
       </c>
       <c r="G48" s="11" t="s">
         <v>201</v>
@@ -5539,30 +5824,30 @@
         <v>202</v>
       </c>
       <c r="I48" s="6" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="J48" s="7" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="6" t="s">
-        <v>136</v>
+        <v>110</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>397</v>
+        <v>111</v>
       </c>
       <c r="C49" s="7" t="s">
         <v>398</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>332</v>
+        <v>216</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>199</v>
+        <v>217</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>333</v>
+        <v>218</v>
       </c>
       <c r="G49" s="11" t="s">
         <v>201</v>
@@ -5579,54 +5864,54 @@
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
-        <v>136</v>
+        <v>110</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>397</v>
+        <v>111</v>
       </c>
       <c r="C50" s="7" t="s">
         <v>401</v>
       </c>
       <c r="D50" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="E50" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="F50" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="G50" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="H50" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="I50" s="6" t="s">
         <v>402</v>
       </c>
-      <c r="E50" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="F50" s="7" t="s">
+      <c r="J50" s="7" t="s">
         <v>403</v>
-      </c>
-      <c r="G50" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="H50" s="11" t="s">
-        <v>202</v>
-      </c>
-      <c r="I50" s="6" t="s">
-        <v>404</v>
-      </c>
-      <c r="J50" s="7" t="s">
-        <v>405</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="6" t="s">
-        <v>140</v>
+        <v>115</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>141</v>
+        <v>404</v>
       </c>
       <c r="C51" s="7" t="s">
+        <v>405</v>
+      </c>
+      <c r="D51" s="6" t="s">
         <v>406</v>
       </c>
-      <c r="D51" s="6" t="s">
-        <v>332</v>
-      </c>
       <c r="E51" s="6" t="s">
-        <v>199</v>
+        <v>407</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>333</v>
+        <v>408</v>
       </c>
       <c r="G51" s="11" t="s">
         <v>201</v>
@@ -5635,30 +5920,30 @@
         <v>202</v>
       </c>
       <c r="I51" s="6" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="J51" s="7" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
-        <v>140</v>
+        <v>115</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>141</v>
+        <v>404</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>332</v>
+        <v>406</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>199</v>
+        <v>407</v>
       </c>
       <c r="F52" s="7" t="s">
-        <v>333</v>
+        <v>408</v>
       </c>
       <c r="G52" s="11" t="s">
         <v>201</v>
@@ -5667,30 +5952,30 @@
         <v>202</v>
       </c>
       <c r="I52" s="6" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="J52" s="7" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" s="6" t="s">
-        <v>145</v>
+        <v>115</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>280</v>
+        <v>307</v>
       </c>
       <c r="E53" s="6" t="s">
         <v>199</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>281</v>
+        <v>308</v>
       </c>
       <c r="G53" s="11" t="s">
         <v>201</v>
@@ -5699,30 +5984,30 @@
         <v>202</v>
       </c>
       <c r="I53" s="6" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="J53" s="7" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" s="6" t="s">
-        <v>145</v>
+        <v>119</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>416</v>
+        <v>406</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>417</v>
+        <v>407</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>418</v>
+        <v>408</v>
       </c>
       <c r="G54" s="11" t="s">
         <v>201</v>
@@ -5734,27 +6019,27 @@
         <v>419</v>
       </c>
       <c r="J54" s="7" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" s="6" t="s">
-        <v>151</v>
+        <v>119</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="C55" s="7" t="s">
         <v>421</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>241</v>
+        <v>406</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>199</v>
+        <v>407</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>242</v>
+        <v>408</v>
       </c>
       <c r="G55" s="11" t="s">
         <v>201</v>
@@ -5771,22 +6056,22 @@
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" s="6" t="s">
-        <v>151</v>
+        <v>119</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="C56" s="7" t="s">
         <v>424</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>241</v>
+        <v>388</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="F56" s="7" t="s">
-        <v>242</v>
+        <v>389</v>
       </c>
       <c r="G56" s="11" t="s">
         <v>201</v>
@@ -5803,22 +6088,22 @@
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="6" t="s">
-        <v>151</v>
+        <v>124</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>212</v>
+        <v>307</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>213</v>
+        <v>199</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>214</v>
+        <v>308</v>
       </c>
       <c r="G57" s="11" t="s">
         <v>201</v>
@@ -5827,62 +6112,62 @@
         <v>202</v>
       </c>
       <c r="I57" s="6" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="J57" s="7" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" s="6" t="s">
-        <v>155</v>
+        <v>124</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="C58" s="7" t="s">
         <v>431</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>432</v>
+        <v>307</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>199</v>
       </c>
       <c r="F58" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="G58" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="H58" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="I58" s="6" t="s">
+        <v>432</v>
+      </c>
+      <c r="J58" s="7" t="s">
         <v>433</v>
-      </c>
-      <c r="G58" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="H58" s="11" t="s">
-        <v>202</v>
-      </c>
-      <c r="I58" s="6" t="s">
-        <v>434</v>
-      </c>
-      <c r="J58" s="7" t="s">
-        <v>435</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" s="6" t="s">
-        <v>155</v>
+        <v>124</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>432</v>
+        <v>307</v>
       </c>
       <c r="E59" s="6" t="s">
         <v>199</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>433</v>
+        <v>308</v>
       </c>
       <c r="G59" s="11" t="s">
         <v>201</v>
@@ -5891,30 +6176,30 @@
         <v>202</v>
       </c>
       <c r="I59" s="6" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="J59" s="7" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" s="6" t="s">
-        <v>159</v>
+        <v>128</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>160</v>
+        <v>437</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>440</v>
+        <v>307</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>199</v>
       </c>
       <c r="F60" s="7" t="s">
-        <v>441</v>
+        <v>308</v>
       </c>
       <c r="G60" s="11" t="s">
         <v>201</v>
@@ -5923,30 +6208,30 @@
         <v>202</v>
       </c>
       <c r="I60" s="6" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="J60" s="7" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" s="6" t="s">
-        <v>159</v>
+        <v>128</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>160</v>
+        <v>437</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>440</v>
+        <v>307</v>
       </c>
       <c r="E61" s="6" t="s">
         <v>199</v>
       </c>
       <c r="F61" s="7" t="s">
-        <v>441</v>
+        <v>308</v>
       </c>
       <c r="G61" s="11" t="s">
         <v>201</v>
@@ -5955,7 +6240,7 @@
         <v>202</v>
       </c>
       <c r="I61" s="6" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="J61" s="7" t="s">
         <v>443</v>
@@ -5963,22 +6248,22 @@
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" s="6" t="s">
-        <v>163</v>
+        <v>128</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="D62" s="6" t="s">
-        <v>448</v>
+        <v>307</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>199</v>
       </c>
       <c r="F62" s="7" t="s">
-        <v>449</v>
+        <v>308</v>
       </c>
       <c r="G62" s="11" t="s">
         <v>201</v>
@@ -5987,30 +6272,30 @@
         <v>202</v>
       </c>
       <c r="I62" s="6" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="J62" s="7" t="s">
-        <v>451</v>
+        <v>443</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" s="6" t="s">
-        <v>163</v>
+        <v>132</v>
       </c>
       <c r="B63" s="6" t="s">
         <v>446</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>453</v>
+        <v>216</v>
       </c>
       <c r="E63" s="6" t="s">
-        <v>454</v>
+        <v>217</v>
       </c>
       <c r="F63" s="7" t="s">
-        <v>455</v>
+        <v>218</v>
       </c>
       <c r="G63" s="11" t="s">
         <v>201</v>
@@ -6019,30 +6304,30 @@
         <v>202</v>
       </c>
       <c r="I63" s="6" t="s">
-        <v>456</v>
+        <v>448</v>
       </c>
       <c r="J63" s="7" t="s">
-        <v>457</v>
+        <v>449</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" s="6" t="s">
-        <v>168</v>
+        <v>132</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>169</v>
+        <v>446</v>
       </c>
       <c r="C64" s="7" t="s">
-        <v>458</v>
+        <v>450</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>459</v>
+        <v>216</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="F64" s="7" t="s">
-        <v>460</v>
+        <v>218</v>
       </c>
       <c r="G64" s="11" t="s">
         <v>201</v>
@@ -6051,30 +6336,30 @@
         <v>202</v>
       </c>
       <c r="I64" s="6" t="s">
-        <v>461</v>
+        <v>451</v>
       </c>
       <c r="J64" s="7" t="s">
-        <v>462</v>
+        <v>452</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" s="6" t="s">
-        <v>174</v>
+        <v>132</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>175</v>
+        <v>446</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>463</v>
+        <v>453</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>464</v>
+        <v>335</v>
       </c>
       <c r="E65" s="6" t="s">
-        <v>465</v>
+        <v>199</v>
       </c>
       <c r="F65" s="7" t="s">
-        <v>466</v>
+        <v>336</v>
       </c>
       <c r="G65" s="11" t="s">
         <v>201</v>
@@ -6083,30 +6368,30 @@
         <v>202</v>
       </c>
       <c r="I65" s="6" t="s">
-        <v>467</v>
+        <v>454</v>
       </c>
       <c r="J65" s="7" t="s">
-        <v>468</v>
+        <v>455</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" s="6" t="s">
-        <v>177</v>
+        <v>136</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>178</v>
+        <v>456</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>469</v>
+        <v>457</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>470</v>
+        <v>458</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>199</v>
       </c>
       <c r="F66" s="7" t="s">
-        <v>471</v>
+        <v>459</v>
       </c>
       <c r="G66" s="11" t="s">
         <v>201</v>
@@ -6115,30 +6400,30 @@
         <v>202</v>
       </c>
       <c r="I66" s="6" t="s">
-        <v>472</v>
+        <v>460</v>
       </c>
       <c r="J66" s="7" t="s">
-        <v>473</v>
+        <v>461</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" s="6" t="s">
-        <v>177</v>
+        <v>136</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>178</v>
+        <v>456</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>474</v>
+        <v>462</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>470</v>
+        <v>463</v>
       </c>
       <c r="E67" s="6" t="s">
         <v>199</v>
       </c>
       <c r="F67" s="7" t="s">
-        <v>471</v>
+        <v>464</v>
       </c>
       <c r="G67" s="11" t="s">
         <v>201</v>
@@ -6147,30 +6432,30 @@
         <v>202</v>
       </c>
       <c r="I67" s="6" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="J67" s="7" t="s">
-        <v>473</v>
+        <v>466</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" s="6" t="s">
-        <v>180</v>
+        <v>136</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>181</v>
+        <v>456</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>476</v>
+        <v>467</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>332</v>
+        <v>468</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>199</v>
       </c>
       <c r="F68" s="7" t="s">
-        <v>333</v>
+        <v>469</v>
       </c>
       <c r="G68" s="11" t="s">
         <v>201</v>
@@ -6179,30 +6464,30 @@
         <v>202</v>
       </c>
       <c r="I68" s="6" t="s">
-        <v>477</v>
+        <v>470</v>
       </c>
       <c r="J68" s="7" t="s">
-        <v>478</v>
+        <v>471</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" s="6" t="s">
-        <v>180</v>
+        <v>140</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>181</v>
+        <v>141</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>479</v>
+        <v>472</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>480</v>
+        <v>361</v>
       </c>
       <c r="E69" s="6" t="s">
         <v>199</v>
       </c>
       <c r="F69" s="7" t="s">
-        <v>481</v>
+        <v>362</v>
       </c>
       <c r="G69" s="11" t="s">
         <v>201</v>
@@ -6211,30 +6496,30 @@
         <v>202</v>
       </c>
       <c r="I69" s="6" t="s">
-        <v>482</v>
+        <v>473</v>
       </c>
       <c r="J69" s="7" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" s="6" t="s">
-        <v>185</v>
+        <v>140</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>186</v>
+        <v>141</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>483</v>
+        <v>475</v>
       </c>
       <c r="D70" s="6" t="s">
-        <v>484</v>
+        <v>361</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>213</v>
+        <v>199</v>
       </c>
       <c r="F70" s="7" t="s">
-        <v>485</v>
+        <v>362</v>
       </c>
       <c r="G70" s="11" t="s">
         <v>201</v>
@@ -6243,42 +6528,938 @@
         <v>202</v>
       </c>
       <c r="I70" s="6" t="s">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="J70" s="7" t="s">
-        <v>487</v>
+        <v>477</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="B71" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="C71" s="7" t="s">
+        <v>478</v>
+      </c>
+      <c r="D71" s="6" t="s">
+        <v>361</v>
+      </c>
+      <c r="E71" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="F71" s="7" t="s">
+        <v>362</v>
+      </c>
+      <c r="G71" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="H71" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="I71" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="J71" s="7" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A72" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="B72" s="6" t="s">
+        <v>481</v>
+      </c>
+      <c r="C72" s="7" t="s">
+        <v>482</v>
+      </c>
+      <c r="D72" s="6" t="s">
+        <v>406</v>
+      </c>
+      <c r="E72" s="6" t="s">
+        <v>407</v>
+      </c>
+      <c r="F72" s="7" t="s">
+        <v>408</v>
+      </c>
+      <c r="G72" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="H72" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="I72" s="6" t="s">
+        <v>483</v>
+      </c>
+      <c r="J72" s="7" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A73" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="B73" s="6" t="s">
+        <v>481</v>
+      </c>
+      <c r="C73" s="7" t="s">
+        <v>485</v>
+      </c>
+      <c r="D73" s="6" t="s">
+        <v>406</v>
+      </c>
+      <c r="E73" s="6" t="s">
+        <v>407</v>
+      </c>
+      <c r="F73" s="7" t="s">
+        <v>408</v>
+      </c>
+      <c r="G73" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="H73" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="I73" s="6" t="s">
+        <v>486</v>
+      </c>
+      <c r="J73" s="7" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A74" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="B74" s="6" t="s">
+        <v>481</v>
+      </c>
+      <c r="C74" s="7" t="s">
+        <v>488</v>
+      </c>
+      <c r="D74" s="6" t="s">
+        <v>458</v>
+      </c>
+      <c r="E74" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="F74" s="7" t="s">
+        <v>459</v>
+      </c>
+      <c r="G74" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="H74" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="I74" s="6" t="s">
+        <v>489</v>
+      </c>
+      <c r="J74" s="7" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A75" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="B75" s="6" t="s">
+        <v>491</v>
+      </c>
+      <c r="C75" s="7" t="s">
+        <v>492</v>
+      </c>
+      <c r="D75" s="6" t="s">
+        <v>493</v>
+      </c>
+      <c r="E75" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="F75" s="7" t="s">
+        <v>494</v>
+      </c>
+      <c r="G75" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="H75" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="I75" s="6" t="s">
+        <v>495</v>
+      </c>
+      <c r="J75" s="7" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A76" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="B76" s="6" t="s">
+        <v>491</v>
+      </c>
+      <c r="C76" s="7" t="s">
+        <v>497</v>
+      </c>
+      <c r="D76" s="6" t="s">
+        <v>493</v>
+      </c>
+      <c r="E76" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="F76" s="7" t="s">
+        <v>494</v>
+      </c>
+      <c r="G76" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="H76" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="I76" s="6" t="s">
+        <v>498</v>
+      </c>
+      <c r="J76" s="7" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A77" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="B77" s="6" t="s">
+        <v>491</v>
+      </c>
+      <c r="C77" s="7" t="s">
+        <v>500</v>
+      </c>
+      <c r="D77" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="E77" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="F77" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="G77" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="H77" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="I77" s="6" t="s">
+        <v>501</v>
+      </c>
+      <c r="J77" s="7" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A78" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="B78" s="6" t="s">
+        <v>503</v>
+      </c>
+      <c r="C78" s="7" t="s">
+        <v>504</v>
+      </c>
+      <c r="D78" s="6" t="s">
+        <v>505</v>
+      </c>
+      <c r="E78" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="F78" s="7" t="s">
+        <v>506</v>
+      </c>
+      <c r="G78" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="H78" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="I78" s="6" t="s">
+        <v>507</v>
+      </c>
+      <c r="J78" s="7" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A79" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="B79" s="6" t="s">
+        <v>503</v>
+      </c>
+      <c r="C79" s="7" t="s">
+        <v>509</v>
+      </c>
+      <c r="D79" s="6" t="s">
+        <v>458</v>
+      </c>
+      <c r="E79" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="F79" s="7" t="s">
+        <v>459</v>
+      </c>
+      <c r="G79" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="H79" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="I79" s="6" t="s">
+        <v>510</v>
+      </c>
+      <c r="J79" s="7" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A80" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="B80" s="6" t="s">
+        <v>503</v>
+      </c>
+      <c r="C80" s="7" t="s">
+        <v>512</v>
+      </c>
+      <c r="D80" s="6" t="s">
+        <v>458</v>
+      </c>
+      <c r="E80" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="F80" s="7" t="s">
+        <v>459</v>
+      </c>
+      <c r="G80" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="H80" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="I80" s="6" t="s">
+        <v>513</v>
+      </c>
+      <c r="J80" s="7" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A81" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="B81" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="C81" s="7" t="s">
+        <v>515</v>
+      </c>
+      <c r="D81" s="6" t="s">
+        <v>516</v>
+      </c>
+      <c r="E81" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="F81" s="7" t="s">
+        <v>517</v>
+      </c>
+      <c r="G81" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="H81" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="I81" s="6" t="s">
+        <v>518</v>
+      </c>
+      <c r="J81" s="7" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A82" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="B82" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="C82" s="7" t="s">
+        <v>520</v>
+      </c>
+      <c r="D82" s="6" t="s">
+        <v>516</v>
+      </c>
+      <c r="E82" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="F82" s="7" t="s">
+        <v>517</v>
+      </c>
+      <c r="G82" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="H82" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="I82" s="6" t="s">
+        <v>521</v>
+      </c>
+      <c r="J82" s="7" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A83" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="B83" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="C83" s="7" t="s">
+        <v>523</v>
+      </c>
+      <c r="D83" s="6" t="s">
+        <v>524</v>
+      </c>
+      <c r="E83" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="F83" s="7" t="s">
+        <v>525</v>
+      </c>
+      <c r="G83" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="H83" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="I83" s="6" t="s">
+        <v>526</v>
+      </c>
+      <c r="J83" s="7" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A84" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="B84" s="6" t="s">
+        <v>528</v>
+      </c>
+      <c r="C84" s="7" t="s">
+        <v>529</v>
+      </c>
+      <c r="D84" s="6" t="s">
+        <v>530</v>
+      </c>
+      <c r="E84" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="F84" s="7" t="s">
+        <v>531</v>
+      </c>
+      <c r="G84" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="H84" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="I84" s="6" t="s">
+        <v>532</v>
+      </c>
+      <c r="J84" s="7" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A85" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="B85" s="6" t="s">
+        <v>528</v>
+      </c>
+      <c r="C85" s="7" t="s">
+        <v>534</v>
+      </c>
+      <c r="D85" s="6" t="s">
+        <v>535</v>
+      </c>
+      <c r="E85" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="F85" s="7" t="s">
+        <v>536</v>
+      </c>
+      <c r="G85" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="H85" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="I85" s="6" t="s">
+        <v>537</v>
+      </c>
+      <c r="J85" s="7" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A86" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="B86" s="6" t="s">
+        <v>528</v>
+      </c>
+      <c r="C86" s="7" t="s">
+        <v>539</v>
+      </c>
+      <c r="D86" s="6" t="s">
+        <v>535</v>
+      </c>
+      <c r="E86" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="F86" s="7" t="s">
+        <v>536</v>
+      </c>
+      <c r="G86" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="H86" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="I86" s="6" t="s">
+        <v>540</v>
+      </c>
+      <c r="J86" s="7" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A87" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="B87" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="C87" s="7" t="s">
+        <v>542</v>
+      </c>
+      <c r="D87" s="6" t="s">
+        <v>543</v>
+      </c>
+      <c r="E87" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="F87" s="7" t="s">
+        <v>544</v>
+      </c>
+      <c r="G87" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="H87" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="I87" s="6" t="s">
+        <v>545</v>
+      </c>
+      <c r="J87" s="7" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A88" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="B88" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="C88" s="7" t="s">
+        <v>547</v>
+      </c>
+      <c r="D88" s="6" t="s">
+        <v>543</v>
+      </c>
+      <c r="E88" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="F88" s="7" t="s">
+        <v>544</v>
+      </c>
+      <c r="G88" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="H88" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="I88" s="6" t="s">
+        <v>548</v>
+      </c>
+      <c r="J88" s="7" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A89" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="B89" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="C89" s="7" t="s">
+        <v>550</v>
+      </c>
+      <c r="D89" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="E89" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="F89" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="G89" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="H89" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="I89" s="6" t="s">
+        <v>551</v>
+      </c>
+      <c r="J89" s="7" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A90" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B90" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="C90" s="7" t="s">
+        <v>553</v>
+      </c>
+      <c r="D90" s="6" t="s">
+        <v>543</v>
+      </c>
+      <c r="E90" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="F90" s="7" t="s">
+        <v>554</v>
+      </c>
+      <c r="G90" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="H90" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="I90" s="6" t="s">
+        <v>555</v>
+      </c>
+      <c r="J90" s="7" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A91" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B91" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="C91" s="7" t="s">
+        <v>557</v>
+      </c>
+      <c r="D91" s="6" t="s">
+        <v>543</v>
+      </c>
+      <c r="E91" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="F91" s="7" t="s">
+        <v>554</v>
+      </c>
+      <c r="G91" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="H91" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="I91" s="6" t="s">
+        <v>558</v>
+      </c>
+      <c r="J91" s="7" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A92" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B92" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="C92" s="7" t="s">
+        <v>560</v>
+      </c>
+      <c r="D92" s="6" t="s">
+        <v>543</v>
+      </c>
+      <c r="E92" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="F92" s="7" t="s">
+        <v>554</v>
+      </c>
+      <c r="G92" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="H92" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="I92" s="6" t="s">
+        <v>561</v>
+      </c>
+      <c r="J92" s="7" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A93" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="B93" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C93" s="7" t="s">
+        <v>562</v>
+      </c>
+      <c r="D93" s="6" t="s">
+        <v>543</v>
+      </c>
+      <c r="E93" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="F93" s="7" t="s">
+        <v>544</v>
+      </c>
+      <c r="G93" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="H93" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="I93" s="6" t="s">
+        <v>563</v>
+      </c>
+      <c r="J93" s="7" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A94" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="B94" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C94" s="7" t="s">
+        <v>565</v>
+      </c>
+      <c r="D94" s="6" t="s">
+        <v>543</v>
+      </c>
+      <c r="E94" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="F94" s="7" t="s">
+        <v>544</v>
+      </c>
+      <c r="G94" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="H94" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="I94" s="6" t="s">
+        <v>566</v>
+      </c>
+      <c r="J94" s="7" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A95" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="B95" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="C95" s="7" t="s">
+        <v>568</v>
+      </c>
+      <c r="D95" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="E95" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="F95" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="G95" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="H95" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="I95" s="6" t="s">
+        <v>569</v>
+      </c>
+      <c r="J95" s="7" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A96" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="B96" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="C96" s="7" t="s">
+        <v>571</v>
+      </c>
+      <c r="D96" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="E96" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="F96" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="G96" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="H96" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="I96" s="6" t="s">
+        <v>572</v>
+      </c>
+      <c r="J96" s="7" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A97" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="B97" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="C97" s="7" t="s">
+        <v>574</v>
+      </c>
+      <c r="D97" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="E97" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="F97" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="G97" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="H97" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="I97" s="6" t="s">
+        <v>575</v>
+      </c>
+      <c r="J97" s="7" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A98" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="B71" s="6" t="s">
+      <c r="B98" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="C71" s="7" t="s">
-        <v>488</v>
-      </c>
-      <c r="D71" s="6" t="s">
-        <v>489</v>
-      </c>
-      <c r="E71" s="6" t="s">
-        <v>465</v>
-      </c>
-      <c r="F71" s="7" t="s">
-        <v>490</v>
-      </c>
-      <c r="G71" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="H71" s="11" t="s">
-        <v>202</v>
-      </c>
-      <c r="I71" s="6" t="s">
-        <v>491</v>
-      </c>
-      <c r="J71" s="7" t="s">
-        <v>492</v>
+      <c r="C98" s="7" t="s">
+        <v>577</v>
+      </c>
+      <c r="D98" s="6" t="s">
+        <v>578</v>
+      </c>
+      <c r="E98" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="F98" s="7" t="s">
+        <v>579</v>
+      </c>
+      <c r="G98" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="H98" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="I98" s="6" t="s">
+        <v>580</v>
+      </c>
+      <c r="J98" s="7" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A99" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="B99" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="C99" s="7" t="s">
+        <v>582</v>
+      </c>
+      <c r="D99" s="6" t="s">
+        <v>583</v>
+      </c>
+      <c r="E99" s="6" t="s">
+        <v>584</v>
+      </c>
+      <c r="F99" s="7" t="s">
+        <v>585</v>
+      </c>
+      <c r="G99" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="H99" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="I99" s="6" t="s">
+        <v>586</v>
+      </c>
+      <c r="J99" s="7" t="s">
+        <v>587</v>
       </c>
     </row>
   </sheetData>
@@ -6423,6 +7604,62 @@
     <hyperlink ref="H70" r:id="rId138"/>
     <hyperlink ref="G71" r:id="rId139"/>
     <hyperlink ref="H71" r:id="rId140"/>
+    <hyperlink ref="G72" r:id="rId141"/>
+    <hyperlink ref="H72" r:id="rId142"/>
+    <hyperlink ref="G73" r:id="rId143"/>
+    <hyperlink ref="H73" r:id="rId144"/>
+    <hyperlink ref="G74" r:id="rId145"/>
+    <hyperlink ref="H74" r:id="rId146"/>
+    <hyperlink ref="G75" r:id="rId147"/>
+    <hyperlink ref="H75" r:id="rId148"/>
+    <hyperlink ref="G76" r:id="rId149"/>
+    <hyperlink ref="H76" r:id="rId150"/>
+    <hyperlink ref="G77" r:id="rId151"/>
+    <hyperlink ref="H77" r:id="rId152"/>
+    <hyperlink ref="G78" r:id="rId153"/>
+    <hyperlink ref="H78" r:id="rId154"/>
+    <hyperlink ref="G79" r:id="rId155"/>
+    <hyperlink ref="H79" r:id="rId156"/>
+    <hyperlink ref="G80" r:id="rId157"/>
+    <hyperlink ref="H80" r:id="rId158"/>
+    <hyperlink ref="G81" r:id="rId159"/>
+    <hyperlink ref="H81" r:id="rId160"/>
+    <hyperlink ref="G82" r:id="rId161"/>
+    <hyperlink ref="H82" r:id="rId162"/>
+    <hyperlink ref="G83" r:id="rId163"/>
+    <hyperlink ref="H83" r:id="rId164"/>
+    <hyperlink ref="G84" r:id="rId165"/>
+    <hyperlink ref="H84" r:id="rId166"/>
+    <hyperlink ref="G85" r:id="rId167"/>
+    <hyperlink ref="H85" r:id="rId168"/>
+    <hyperlink ref="G86" r:id="rId169"/>
+    <hyperlink ref="H86" r:id="rId170"/>
+    <hyperlink ref="G87" r:id="rId171"/>
+    <hyperlink ref="H87" r:id="rId172"/>
+    <hyperlink ref="G88" r:id="rId173"/>
+    <hyperlink ref="H88" r:id="rId174"/>
+    <hyperlink ref="G89" r:id="rId175"/>
+    <hyperlink ref="H89" r:id="rId176"/>
+    <hyperlink ref="G90" r:id="rId177"/>
+    <hyperlink ref="H90" r:id="rId178"/>
+    <hyperlink ref="G91" r:id="rId179"/>
+    <hyperlink ref="H91" r:id="rId180"/>
+    <hyperlink ref="G92" r:id="rId181"/>
+    <hyperlink ref="H92" r:id="rId182"/>
+    <hyperlink ref="G93" r:id="rId183"/>
+    <hyperlink ref="H93" r:id="rId184"/>
+    <hyperlink ref="G94" r:id="rId185"/>
+    <hyperlink ref="H94" r:id="rId186"/>
+    <hyperlink ref="G95" r:id="rId187"/>
+    <hyperlink ref="H95" r:id="rId188"/>
+    <hyperlink ref="G96" r:id="rId189"/>
+    <hyperlink ref="H96" r:id="rId190"/>
+    <hyperlink ref="G97" r:id="rId191"/>
+    <hyperlink ref="H97" r:id="rId192"/>
+    <hyperlink ref="G98" r:id="rId193"/>
+    <hyperlink ref="H98" r:id="rId194"/>
+    <hyperlink ref="G99" r:id="rId195"/>
+    <hyperlink ref="H99" r:id="rId196"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -6441,90 +7678,90 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>493</v>
+        <v>588</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>494</v>
+        <v>589</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>495</v>
+        <v>590</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>496</v>
+        <v>591</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>497</v>
+        <v>592</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>498</v>
+        <v>593</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>499</v>
+        <v>594</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>500</v>
+        <v>595</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>501</v>
+        <v>596</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>502</v>
+        <v>597</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>503</v>
+        <v>598</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>504</v>
+        <v>599</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>505</v>
+        <v>600</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>506</v>
+        <v>601</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>507</v>
+        <v>602</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>508</v>
+        <v>603</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>509</v>
+        <v>604</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>510</v>
+        <v>605</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>511</v>
+        <v>606</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>512</v>
+        <v>607</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>513</v>
+        <v>608</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>514</v>
+        <v>609</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>515</v>
+        <v>610</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>516</v>
+        <v>611</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -6540,46 +7777,46 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>517</v>
+        <v>612</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>518</v>
+        <v>613</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>519</v>
+        <v>614</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>520</v>
+        <v>615</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>521</v>
+        <v>616</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>519</v>
+        <v>614</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>522</v>
+        <v>617</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>523</v>
+        <v>618</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>519</v>
+        <v>614</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>524</v>
+        <v>619</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>525</v>
+        <v>620</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>526</v>
+        <v>621</v>
       </c>
     </row>
   </sheetData>

--- a/content/research/cars-research-2026-10.xlsx
+++ b/content/research/cars-research-2026-10.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1313" uniqueCount="622">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1243" uniqueCount="595">
   <si>
     <t>بحث أسعار وصور سيارات المعرض — تشرين الأول 2026</t>
   </si>
@@ -31,7 +31,7 @@
     <t>• ورقة «الأسعار»: لكل سيارة من الـ 34 بالملف، سعرها بسوق العراق من إعلانات حقيقية (الوسيط، أقل وأعلى سعر، عدد الإعلانات) مع روابط المصادر، والسعر المقترح بالدينار.</t>
   </si>
   <si>
-    <t>• ورقة «الصور»: 98 صورة حقيقية مرخّصة من ويكيميديا كومنز لنفس الموديلات والأجيال (بحث 26 تشرين الأول 2026، مع التحقق من الرخصة والمقاس عبر Commons API)، مع اسم المصوّر ونوع الرخصة ونص الإسناد الجاهز. الصور الرسمية لمواقع الشركات لم تُستخدم لأن شروطها تحصرها بالاستخدام الصحفي.</t>
+    <t>• ورقة «الصور»: 91 صورة حقيقية مرخّصة من ويكيميديا كومنز لنفس الموديلات والأجيال (بحث 26 تشرين الأول 2026، مع التحقق من الرخصة والمقاس عبر Commons API)، مع اسم المصوّر ونوع الرخصة ونص الإسناد الجاهز. الصور الرسمية لمواقع الشركات لم تُستخدم لأن شروطها تحصرها بالاستخدام الصحفي.</t>
   </si>
   <si>
     <t>• ورقة «الوكلاء والتمويل»: الوكلاء الرسميون للماركات الصينية بالعراق وعروض التمويل المصرفية المنشورة.</t>
@@ -665,6 +665,30 @@
     <t>Toyota Camry 2024</t>
   </si>
   <si>
+    <t>24 Toyota Camry SE.jpg</t>
+  </si>
+  <si>
+    <t>HJUdall</t>
+  </si>
+  <si>
+    <t>CC0</t>
+  </si>
+  <si>
+    <t>HJUdall / Wikimedia Commons (CC0)</t>
+  </si>
+  <si>
+    <t>فتح</t>
+  </si>
+  <si>
+    <t>تحميل</t>
+  </si>
+  <si>
+    <t>car-001-1.webp</t>
+  </si>
+  <si>
+    <t>Exact 2024 SE. Color and angle not stated; check visually. Shot on a dealer lot by a Commons user (photo is the uploader's own work, not taken from a dealer website).</t>
+  </si>
+  <si>
     <t>2022 Toyota Camry SE Standard Package in Celestial Silver Metallic, Front Left.jpg</t>
   </si>
   <si>
@@ -677,13 +701,7 @@
     <t>الصورة: Elise240SX / Wikimedia Commons — CC BY-SA 4.0</t>
   </si>
   <si>
-    <t>فتح</t>
-  </si>
-  <si>
-    <t>تحميل</t>
-  </si>
-  <si>
-    <t>car-001-1.webp</t>
+    <t>car-001-2.webp</t>
   </si>
   <si>
     <t>2022 SE, same XV70 2021+ facelift as 2024 SE. Color differs from requested red.</t>
@@ -692,33 +710,39 @@
     <t>2022 Toyota Camry SE Standard Package in Celestial Silver Metallic, Rear Left.jpg</t>
   </si>
   <si>
-    <t>car-001-2.webp</t>
+    <t>car-001-3.webp</t>
   </si>
   <si>
     <t>Same car as car-001-1. Color differs from requested red.</t>
   </si>
   <si>
-    <t>24 Toyota Camry SE.jpg</t>
-  </si>
-  <si>
-    <t>HJUdall</t>
-  </si>
-  <si>
-    <t>CC0</t>
-  </si>
-  <si>
-    <t>HJUdall / Wikimedia Commons (CC0)</t>
-  </si>
-  <si>
-    <t>car-001-3.webp</t>
-  </si>
-  <si>
-    <t>Exact 2024 SE. Color and angle not stated; check visually. Shot on a dealer lot by a Commons user (photo is the uploader's own work, not taken from a dealer website).</t>
-  </si>
-  <si>
     <t>Toyota Corolla 2023</t>
   </si>
   <si>
+    <t>2025 Toyota Corolla LE ice cap.jpg</t>
+  </si>
+  <si>
+    <t>Rachelhoots</t>
+  </si>
+  <si>
+    <t>الصورة: Rachelhoots / Wikimedia Commons — CC BY-SA 4.0</t>
+  </si>
+  <si>
+    <t>car-002-1.webp</t>
+  </si>
+  <si>
+    <t>2025 LE, same 2023+ facelift. White as requested; angle not stated, check visually.</t>
+  </si>
+  <si>
+    <t>24 Toyota Corolla XSE.jpg</t>
+  </si>
+  <si>
+    <t>car-002-2.webp</t>
+  </si>
+  <si>
+    <t>2024 XSE shares the SE sport front fascia; nearest match to SE trim found. Color/angle not stated; check visually.</t>
+  </si>
+  <si>
     <t>2024 Toyota Corolla LE in Classic Silver Metallic, front right.jpg</t>
   </si>
   <si>
@@ -731,36 +755,12 @@
     <t>الصورة: Mr.choppers / Wikimedia Commons — CC BY-SA 3.0</t>
   </si>
   <si>
-    <t>car-002-1.webp</t>
+    <t>car-002-3.webp</t>
   </si>
   <si>
     <t>2024 LE, same E210 2023 facelift. LE front bumper differs from SE/XSE sport fascia. Color differs from requested white.</t>
   </si>
   <si>
-    <t>2025 Toyota Corolla LE ice cap.jpg</t>
-  </si>
-  <si>
-    <t>Rachelhoots</t>
-  </si>
-  <si>
-    <t>الصورة: Rachelhoots / Wikimedia Commons — CC BY-SA 4.0</t>
-  </si>
-  <si>
-    <t>car-002-2.webp</t>
-  </si>
-  <si>
-    <t>2025 LE, same 2023+ facelift. White as requested; angle not stated, check visually.</t>
-  </si>
-  <si>
-    <t>24 Toyota Corolla XSE.jpg</t>
-  </si>
-  <si>
-    <t>car-002-3.webp</t>
-  </si>
-  <si>
-    <t>2024 XSE shares the SE sport front fascia; nearest match to SE trim found. Color/angle not stated; check visually.</t>
-  </si>
-  <si>
     <t>Toyota Land Cruiser 2026</t>
   </si>
   <si>
@@ -839,21 +839,6 @@
     <t>Same car/series as car-004-1.</t>
   </si>
   <si>
-    <t>Toyota Land Cruiser Prado J150 LWB facelift Sanming 01 2023-02-16.jpg</t>
-  </si>
-  <si>
-    <t>JamesYoung8167</t>
-  </si>
-  <si>
-    <t>الصورة: JamesYoung8167 / Wikimedia Commons — CC BY-SA 4.0</t>
-  </si>
-  <si>
-    <t>car-004-3.webp</t>
-  </si>
-  <si>
-    <t>J150 5-door facelift photographed in China. Confirm it is the 2017.9+ final facelift face, not the 2013 one.</t>
-  </si>
-  <si>
     <t>Kia K5 2024</t>
   </si>
   <si>
@@ -1094,6 +1079,15 @@
     <t>Nissan Patrol 2026</t>
   </si>
   <si>
+    <t>Nissan Patrol Y63 3.5 V6T LE Granite Black - rear.jpg</t>
+  </si>
+  <si>
+    <t>car-012-1.webp</t>
+  </si>
+  <si>
+    <t>Philippine-market Y63 3.5 V6T LE in black.</t>
+  </si>
+  <si>
     <t>Nissan Patrol 2025 Y63.jpg</t>
   </si>
   <si>
@@ -1103,21 +1097,12 @@
     <t>ToyGTone / Wikimedia Commons (CC0)</t>
   </si>
   <si>
-    <t>car-012-1.webp</t>
+    <t>car-012-2.webp</t>
   </si>
   <si>
     <t>2025 Patrol LE Platinum V6T (Y63) photographed in a Nissan showroom in Bahrain (GCC spec, exact trim). Photo is the uploader's own work. Color/angle not stated.</t>
   </si>
   <si>
-    <t>Nissan Patrol Y63 3.5 V6T LE Granite Black - rear.jpg</t>
-  </si>
-  <si>
-    <t>car-012-2.webp</t>
-  </si>
-  <si>
-    <t>Philippine-market Y63 3.5 V6T LE in black.</t>
-  </si>
-  <si>
     <t>Nissan Patrol Y63 3.5 V6T LE interior view.jpg</t>
   </si>
   <si>
@@ -1127,6 +1112,30 @@
     <t>Philippine-market Y63 LE interior.</t>
   </si>
   <si>
+    <t>23 Nissan Versa SR.jpg</t>
+  </si>
+  <si>
+    <t>car-013-1.webp</t>
+  </si>
+  <si>
+    <t>2023 US Versa SR. Shot on a dealer lot by a Commons user.</t>
+  </si>
+  <si>
+    <t>2023 Nissan Versa (N18) IMG 3105.jpg</t>
+  </si>
+  <si>
+    <t>Alexander Migl</t>
+  </si>
+  <si>
+    <t>الصورة: Alexander Migl / Wikimedia Commons — CC BY-SA 4.0</t>
+  </si>
+  <si>
+    <t>car-013-2.webp</t>
+  </si>
+  <si>
+    <t>2023 Versa (N18). Check angle.</t>
+  </si>
+  <si>
     <t>2024 Nissan Versa front view.jpg</t>
   </si>
   <si>
@@ -1139,36 +1148,12 @@
     <t>الصورة: Deathpallie325 / Wikimedia Commons — CC BY 4.0</t>
   </si>
   <si>
-    <t>car-013-1.webp</t>
+    <t>car-013-3.webp</t>
   </si>
   <si>
     <t>2024 US Versa SR (N18, same car as GCC Sunny). US Versa had a 2023 refresh; confirm the GCC 2024 Sunny uses the same front.</t>
   </si>
   <si>
-    <t>23 Nissan Versa SR.jpg</t>
-  </si>
-  <si>
-    <t>car-013-2.webp</t>
-  </si>
-  <si>
-    <t>2023 US Versa SR. Shot on a dealer lot by a Commons user.</t>
-  </si>
-  <si>
-    <t>2023 Nissan Versa (N18) IMG 3105.jpg</t>
-  </si>
-  <si>
-    <t>Alexander Migl</t>
-  </si>
-  <si>
-    <t>الصورة: Alexander Migl / Wikimedia Commons — CC BY-SA 4.0</t>
-  </si>
-  <si>
-    <t>car-013-3.webp</t>
-  </si>
-  <si>
-    <t>2023 Versa (N18). Check angle.</t>
-  </si>
-  <si>
     <t>Chevrolet Malibu 2023</t>
   </si>
   <si>
@@ -1193,10 +1178,19 @@
     <t>Chevrolet Tahoe 2023</t>
   </si>
   <si>
+    <t>Chevrolet Tahoe GMT1UC 5.3 Z71 V8 Black.jpg</t>
+  </si>
+  <si>
+    <t>car-015-1.webp</t>
+  </si>
+  <si>
+    <t>5th gen pre-facelift 5.3 V8 in requested black; Z71 trim (off-road front bumper differs from LT). Philippine market.</t>
+  </si>
+  <si>
     <t>2022 Chevrolet Tahoe RST, front 3.7.22.jpg</t>
   </si>
   <si>
-    <t>car-015-1.webp</t>
+    <t>car-015-2.webp</t>
   </si>
   <si>
     <t>2022 Tahoe = 5th gen (GMT T1XX) pre-facelift, same as 2023. RST trim (body-colour grille) rather than LT.</t>
@@ -1205,21 +1199,12 @@
     <t>2022 Chevrolet Tahoe RST, rear 3.7.22.jpg</t>
   </si>
   <si>
-    <t>car-015-2.webp</t>
+    <t>car-015-3.webp</t>
   </si>
   <si>
     <t>Same car as car-015-1.</t>
   </si>
   <si>
-    <t>Chevrolet Tahoe GMT1UC 5.3 Z71 V8 Black.jpg</t>
-  </si>
-  <si>
-    <t>car-015-3.webp</t>
-  </si>
-  <si>
-    <t>5th gen pre-facelift 5.3 V8 in requested black; Z71 trim (off-road front bumper differs from LT). Philippine market.</t>
-  </si>
-  <si>
     <t>2024 Lexus ES Sedan.jpg</t>
   </si>
   <si>
@@ -1235,7 +1220,94 @@
     <t>2024 ES = XZ10 2022+ facelift. Photographed outside a Lexus dealership by a Commons user. Check angle/color.</t>
   </si>
   <si>
-    <t>Lexus ES 300h (2023) (54742901894).jpg</t>
+    <t>2024 Lexus ES in Sunlit Green.jpg</t>
+  </si>
+  <si>
+    <t>car-016-2.webp</t>
+  </si>
+  <si>
+    <t>2024 ES facelift. Color differs from requested white.</t>
+  </si>
+  <si>
+    <t>2023 Lexus RX 350 Premium Plus in Matador Red Mica, front left.jpg</t>
+  </si>
+  <si>
+    <t>car-017-1.webp</t>
+  </si>
+  <si>
+    <t>2023 RX 350 2.4T AWD (AL30). Color differs from requested blue; no blue AL30 found.</t>
+  </si>
+  <si>
+    <t>2023 Lexus RX 350 Premium Plus in Matador Red Mica, rear left.jpg</t>
+  </si>
+  <si>
+    <t>car-017-2.webp</t>
+  </si>
+  <si>
+    <t>Same car as car-017-1.</t>
+  </si>
+  <si>
+    <t>23 Lexus RX 350 Premium.jpg</t>
+  </si>
+  <si>
+    <t>car-017-3.webp</t>
+  </si>
+  <si>
+    <t>2023 RX 350 (AL30). Shot on a dealer lot by a Commons user. Check color/angle.</t>
+  </si>
+  <si>
+    <t>Mercedes C 300 2024</t>
+  </si>
+  <si>
+    <t>Mercedes-Benz W206 C 300 4MATIC AMG Line Polar White (4).jpg</t>
+  </si>
+  <si>
+    <t>car-018-1.webp</t>
+  </si>
+  <si>
+    <t>W206 C 300 4MATIC AMG Line in requested white (Korean market). Check angle; other numbers in the same series give more angles.</t>
+  </si>
+  <si>
+    <t>Mercedes-Benz C 300 d AMG Line (W 206) – f 10032024.jpg</t>
+  </si>
+  <si>
+    <t>© M 93</t>
+  </si>
+  <si>
+    <t>CC BY-SA 3.0 de</t>
+  </si>
+  <si>
+    <t>الصورة: © M 93 / Wikimedia Commons — CC BY-SA 3.0 de</t>
+  </si>
+  <si>
+    <t>car-018-2.webp</t>
+  </si>
+  <si>
+    <t>W206 C 300 d AMG Line (European diesel) - same body/AMG Line styling as US C 300; badge differs.</t>
+  </si>
+  <si>
+    <t>Mercedes GLE 450 2026</t>
+  </si>
+  <si>
+    <t>Mercedes-Benz GLE AMG Line (V 167, Facelift) – f 14042024.jpg</t>
+  </si>
+  <si>
+    <t>car-019-1.webp</t>
+  </si>
+  <si>
+    <t>V167 facelift (stated in title), AMG Line, European market. Engine variant not stated.</t>
+  </si>
+  <si>
+    <t>Mercedes-Benz GLE AMG Line (V 167, Facelift) – h 14042024.jpg</t>
+  </si>
+  <si>
+    <t>car-019-2.webp</t>
+  </si>
+  <si>
+    <t>Same car as car-019-1.</t>
+  </si>
+  <si>
+    <t>Mercedes-Benz GLE 450 4MATIC (W167, 2026) (55211989821).jpg</t>
   </si>
   <si>
     <t>Charles from Port Chester, New York</t>
@@ -1244,111 +1316,6 @@
     <t>Charles from Port Chester, New York / Wikimedia Commons (CC0)</t>
   </si>
   <si>
-    <t>car-016-2.webp</t>
-  </si>
-  <si>
-    <t>2023 ES 300h - same facelift body as ES 350 (badging differs). Flickr import.</t>
-  </si>
-  <si>
-    <t>2024 Lexus ES in Sunlit Green.jpg</t>
-  </si>
-  <si>
-    <t>car-016-3.webp</t>
-  </si>
-  <si>
-    <t>2024 ES facelift. Color differs from requested white.</t>
-  </si>
-  <si>
-    <t>2023 Lexus RX 350 Premium Plus in Matador Red Mica, front left.jpg</t>
-  </si>
-  <si>
-    <t>car-017-1.webp</t>
-  </si>
-  <si>
-    <t>2023 RX 350 2.4T AWD (AL30). Color differs from requested blue; no blue AL30 found.</t>
-  </si>
-  <si>
-    <t>2023 Lexus RX 350 Premium Plus in Matador Red Mica, rear left.jpg</t>
-  </si>
-  <si>
-    <t>car-017-2.webp</t>
-  </si>
-  <si>
-    <t>Same car as car-017-1.</t>
-  </si>
-  <si>
-    <t>23 Lexus RX 350 Premium.jpg</t>
-  </si>
-  <si>
-    <t>car-017-3.webp</t>
-  </si>
-  <si>
-    <t>2023 RX 350 (AL30). Shot on a dealer lot by a Commons user. Check color/angle.</t>
-  </si>
-  <si>
-    <t>Mercedes C 300 2024</t>
-  </si>
-  <si>
-    <t>Mercedes-Benz C 300 d AMG Line (W 206) – f 10032024.jpg</t>
-  </si>
-  <si>
-    <t>© M 93</t>
-  </si>
-  <si>
-    <t>CC BY-SA 3.0 de</t>
-  </si>
-  <si>
-    <t>الصورة: © M 93 / Wikimedia Commons — CC BY-SA 3.0 de</t>
-  </si>
-  <si>
-    <t>car-018-1.webp</t>
-  </si>
-  <si>
-    <t>W206 C 300 d AMG Line (European diesel) - same body/AMG Line styling as US C 300; badge differs.</t>
-  </si>
-  <si>
-    <t>Mercedes-Benz C 300 d AMG Line (W 206) – h 10032024.jpg</t>
-  </si>
-  <si>
-    <t>car-018-2.webp</t>
-  </si>
-  <si>
-    <t>Same car as car-018-1. Rear badge reads 300 d.</t>
-  </si>
-  <si>
-    <t>Mercedes-Benz W206 C 300 4MATIC AMG Line Polar White (4).jpg</t>
-  </si>
-  <si>
-    <t>car-018-3.webp</t>
-  </si>
-  <si>
-    <t>W206 C 300 4MATIC AMG Line in requested white (Korean market). Check angle; other numbers in the same series give more angles.</t>
-  </si>
-  <si>
-    <t>Mercedes GLE 450 2026</t>
-  </si>
-  <si>
-    <t>Mercedes-Benz GLE AMG Line (V 167, Facelift) – f 14042024.jpg</t>
-  </si>
-  <si>
-    <t>car-019-1.webp</t>
-  </si>
-  <si>
-    <t>V167 facelift (stated in title), AMG Line, European market. Engine variant not stated.</t>
-  </si>
-  <si>
-    <t>Mercedes-Benz GLE AMG Line (V 167, Facelift) – h 14042024.jpg</t>
-  </si>
-  <si>
-    <t>car-019-2.webp</t>
-  </si>
-  <si>
-    <t>Same car as car-019-1.</t>
-  </si>
-  <si>
-    <t>Mercedes-Benz GLE 450 4MATIC (W167, 2026) (55211989821).jpg</t>
-  </si>
-  <si>
     <t>car-019-3.webp</t>
   </si>
   <si>
@@ -1445,7 +1412,70 @@
     <t>Land Rover Defender 2024</t>
   </si>
   <si>
-    <t>Land Rover Defender 110 (L663) 1X7A1919.jpg</t>
+    <t>Land Rover Defender 110 First Edition 2020 - rear.jpg</t>
+  </si>
+  <si>
+    <t>DeFacto</t>
+  </si>
+  <si>
+    <t>الصورة: DeFacto / Wikimedia Commons — CC BY-SA 4.0</t>
+  </si>
+  <si>
+    <t>car-023-1.webp</t>
+  </si>
+  <si>
+    <t>2020 Defender 110 First Edition (L663) - same body as 2024 110.</t>
+  </si>
+  <si>
+    <t>2024 Kia Picanto (JA) Rutesheimer Autoschau 2025 DSC 9198.jpg</t>
+  </si>
+  <si>
+    <t>car-024-1.webp</t>
+  </si>
+  <si>
+    <t>2024 Picanto JA (2024 facelift), European market. Check angle/color.</t>
+  </si>
+  <si>
+    <t>2024 Kia Picanto (JA) Rutesheimer Autoschau 2025 DSC 9200.jpg</t>
+  </si>
+  <si>
+    <t>car-024-2.webp</t>
+  </si>
+  <si>
+    <t>Same car/event as car-024-1. Check angle.</t>
+  </si>
+  <si>
+    <t>2024 Kia Picanto (JA) IAA 2025 DSC 1272.jpg</t>
+  </si>
+  <si>
+    <t>car-024-3.webp</t>
+  </si>
+  <si>
+    <t>2024 Picanto JA facelift at IAA 2025 (motor show stand - check background for signage).</t>
+  </si>
+  <si>
+    <t>Kia EV6 2026</t>
+  </si>
+  <si>
+    <t>Kia EV6 GT-line (Facelift) – f 27072025.jpg</t>
+  </si>
+  <si>
+    <t>car-025-1.webp</t>
+  </si>
+  <si>
+    <t>EV6 GT-Line facelift (2025+), European market.</t>
+  </si>
+  <si>
+    <t>Kia EV6 GT-line (Facelift) – h 27072025.jpg</t>
+  </si>
+  <si>
+    <t>car-025-2.webp</t>
+  </si>
+  <si>
+    <t>Same car as car-025-1.</t>
+  </si>
+  <si>
+    <t>2025 Kia EV6 GT-Line Auto Zuerich 2024 DSC 6468.jpg</t>
   </si>
   <si>
     <t>Alexander-93</t>
@@ -1454,93 +1484,6 @@
     <t>الصورة: Alexander-93 / Wikimedia Commons — CC BY-SA 4.0</t>
   </si>
   <si>
-    <t>car-023-1.webp</t>
-  </si>
-  <si>
-    <t>L663 110 body. Trim not stated. Check angle/color; no white X-Dynamic SE found.</t>
-  </si>
-  <si>
-    <t>Land Rover Defender 110 First Edition 2020 - rear.jpg</t>
-  </si>
-  <si>
-    <t>DeFacto</t>
-  </si>
-  <si>
-    <t>الصورة: DeFacto / Wikimedia Commons — CC BY-SA 4.0</t>
-  </si>
-  <si>
-    <t>car-023-2.webp</t>
-  </si>
-  <si>
-    <t>2020 Defender 110 First Edition (L663) - same body as 2024 110.</t>
-  </si>
-  <si>
-    <t>Land Rover DEFENDER 110 S ADVENTURE PACK (3BA-LE72XAA) interior.jpg</t>
-  </si>
-  <si>
-    <t>Tokumeigakarinoaoshima</t>
-  </si>
-  <si>
-    <t>الصورة: Tokumeigakarinoaoshima / Wikimedia Commons — CC BY-SA 4.0</t>
-  </si>
-  <si>
-    <t>car-023-3.webp</t>
-  </si>
-  <si>
-    <t>Japanese-market 110 S interior (right-hand drive - GCC cars are left-hand drive).</t>
-  </si>
-  <si>
-    <t>2024 Kia Picanto (JA) Rutesheimer Autoschau 2025 DSC 9198.jpg</t>
-  </si>
-  <si>
-    <t>car-024-1.webp</t>
-  </si>
-  <si>
-    <t>2024 Picanto JA (2024 facelift), European market. Check angle/color.</t>
-  </si>
-  <si>
-    <t>2024 Kia Picanto (JA) Rutesheimer Autoschau 2025 DSC 9200.jpg</t>
-  </si>
-  <si>
-    <t>car-024-2.webp</t>
-  </si>
-  <si>
-    <t>Same car/event as car-024-1. Check angle.</t>
-  </si>
-  <si>
-    <t>2024 Kia Picanto (JA) IAA 2025 DSC 1272.jpg</t>
-  </si>
-  <si>
-    <t>car-024-3.webp</t>
-  </si>
-  <si>
-    <t>2024 Picanto JA facelift at IAA 2025 (motor show stand - check background for signage).</t>
-  </si>
-  <si>
-    <t>Kia EV6 2026</t>
-  </si>
-  <si>
-    <t>Kia EV6 GT-line (Facelift) – f 27072025.jpg</t>
-  </si>
-  <si>
-    <t>car-025-1.webp</t>
-  </si>
-  <si>
-    <t>EV6 GT-Line facelift (2025+), European market.</t>
-  </si>
-  <si>
-    <t>Kia EV6 GT-line (Facelift) – h 27072025.jpg</t>
-  </si>
-  <si>
-    <t>car-025-2.webp</t>
-  </si>
-  <si>
-    <t>Same car as car-025-1.</t>
-  </si>
-  <si>
-    <t>2025 Kia EV6 GT-Line Auto Zuerich 2024 DSC 6468.jpg</t>
-  </si>
-  <si>
     <t>car-025-3.webp</t>
   </si>
   <si>
@@ -1586,6 +1529,24 @@
     <t>Honda Civic 2023</t>
   </si>
   <si>
+    <t>Honda Civic (2021) sedan Sport DSC 7057.jpg</t>
+  </si>
+  <si>
+    <t>car-027-1.webp</t>
+  </si>
+  <si>
+    <t>11th gen sedan Sport. Check angle/color.</t>
+  </si>
+  <si>
+    <t>Honda Civic (2021) sedan Sport DSC 7054.jpg</t>
+  </si>
+  <si>
+    <t>car-027-2.webp</t>
+  </si>
+  <si>
+    <t>Same car as car-027-2. Check angle.</t>
+  </si>
+  <si>
     <t>2022 Honda Civic Sport, Front Right, 06-20-2021.jpg</t>
   </si>
   <si>
@@ -1595,69 +1556,36 @@
     <t>الصورة: SsmIntrigue / Wikimedia Commons — CC BY-SA 4.0</t>
   </si>
   <si>
-    <t>car-027-1.webp</t>
+    <t>car-027-3.webp</t>
   </si>
   <si>
     <t>11th gen sedan, Sport trim, North American. 2022 = same pre-refresh body as 2023.</t>
   </si>
   <si>
-    <t>Honda Civic (2021) sedan Sport DSC 7057.jpg</t>
-  </si>
-  <si>
-    <t>car-027-2.webp</t>
-  </si>
-  <si>
-    <t>11th gen sedan Sport. Check angle/color.</t>
-  </si>
-  <si>
-    <t>Honda Civic (2021) sedan Sport DSC 7054.jpg</t>
-  </si>
-  <si>
-    <t>car-027-3.webp</t>
-  </si>
-  <si>
-    <t>Same car as car-027-2. Check angle.</t>
+    <t>Mitsubishi Pajero CN Spec V6 3.0L(After Second Facelift)02.jpg</t>
+  </si>
+  <si>
+    <t>Tangjunwen CN</t>
+  </si>
+  <si>
+    <t>الصورة: Tangjunwen CN / Wikimedia Commons — CC BY-SA 4.0</t>
+  </si>
+  <si>
+    <t>car-028-1.webp</t>
+  </si>
+  <si>
+    <t>Same car as car-028-1.</t>
   </si>
   <si>
     <t>Mitsubishi Pajero CN Spec V6 3.0L(After Second Facelift)01.jpg</t>
   </si>
   <si>
-    <t>Tangjunwen CN</t>
-  </si>
-  <si>
-    <t>الصورة: Tangjunwen CN / Wikimedia Commons — CC BY-SA 4.0</t>
-  </si>
-  <si>
-    <t>car-028-1.webp</t>
+    <t>car-028-2.webp</t>
   </si>
   <si>
     <t>4th gen Pajero after its second (final) facelift, Chinese-spec 3.0 V6. Confirm it is the long-wheelbase 5-door body. Check angle/color.</t>
   </si>
   <si>
-    <t>Mitsubishi Pajero CN Spec V6 3.0L(After Second Facelift)02.jpg</t>
-  </si>
-  <si>
-    <t>car-028-2.webp</t>
-  </si>
-  <si>
-    <t>Same car as car-028-1.</t>
-  </si>
-  <si>
-    <t>2019 pajero final edition interior.jpg</t>
-  </si>
-  <si>
-    <t>マッドキラー</t>
-  </si>
-  <si>
-    <t>الصورة: マッドキラー / Wikimedia Commons — CC BY-SA 4.0</t>
-  </si>
-  <si>
-    <t>car-028-3.webp</t>
-  </si>
-  <si>
-    <t>2019 Japanese Pajero Final Edition interior (right-hand drive - GCC cars are left-hand drive).</t>
-  </si>
-  <si>
     <t>Toyota Hilux 2024</t>
   </si>
   <si>
@@ -1676,7 +1604,7 @@
     <t>8th gen 2020+ facelift double cab (Thai Revo Z-Edition). Front bumper/grille differ from GCC 2.7 base trims. Photographed at a Toyota showroom by a Commons user.</t>
   </si>
   <si>
-    <t>Toyota Hilux 4x2 G 2022.jpg</t>
+    <t>Toyota Hilux 4x2 G 2024 (2).jpg</t>
   </si>
   <si>
     <t>Captainmorlypogi1959</t>
@@ -1688,18 +1616,18 @@
     <t>car-029-2.webp</t>
   </si>
   <si>
-    <t>Philippine 2022 Hilux G double cab, 2020+ facelift. Check angle/color.</t>
-  </si>
-  <si>
-    <t>Toyota Hilux 4x2 G 2024 (2).jpg</t>
-  </si>
-  <si>
-    <t>car-029-3.webp</t>
-  </si>
-  <si>
     <t>Philippine 2024 Hilux G (street shot). Check angle and that the whole car is in frame.</t>
   </si>
   <si>
+    <t>Moscow, Changan CS75 plus grey, May 2026 02.jpg</t>
+  </si>
+  <si>
+    <t>car-030-1.webp</t>
+  </si>
+  <si>
+    <t>Requested color. Generation NOT stated in metadata - street photo in Moscow 2026; confirm it is the 3rd gen before use.</t>
+  </si>
+  <si>
     <t>Changan CS75 Plus III 001.jpg</t>
   </si>
   <si>
@@ -1709,7 +1637,7 @@
     <t>JustAnotherCarDesigner / Wikimedia Commons (CC0)</t>
   </si>
   <si>
-    <t>car-030-1.webp</t>
+    <t>car-030-2.webp</t>
   </si>
   <si>
     <t>3rd gen CS75 Plus (stated in title), China. Note: the same uploader has a separate 2026 facelift set; confirm which face the Middle East 2026 car uses.</t>
@@ -1718,21 +1646,12 @@
     <t>Changan CS75 Plus III 002.jpg</t>
   </si>
   <si>
-    <t>car-030-2.webp</t>
+    <t>car-030-3.webp</t>
   </si>
   <si>
     <t>Same series as car-030-1.</t>
   </si>
   <si>
-    <t>Moscow, Changan CS75 plus grey, May 2026 02.jpg</t>
-  </si>
-  <si>
-    <t>car-030-3.webp</t>
-  </si>
-  <si>
-    <t>Requested color. Generation NOT stated in metadata - street photo in Moscow 2026; confirm it is the 3rd gen before use.</t>
-  </si>
-  <si>
     <t>Geely Binyue Cool 001.jpg</t>
   </si>
   <si>
@@ -1760,22 +1679,22 @@
     <t>car-031-3.webp</t>
   </si>
   <si>
+    <t>Haval H6 III facelift 001.jpg</t>
+  </si>
+  <si>
+    <t>car-032-1.webp</t>
+  </si>
+  <si>
+    <t>Same series as car-032-1.</t>
+  </si>
+  <si>
     <t>Haval H6 III facelift 002.jpg</t>
   </si>
   <si>
-    <t>car-032-1.webp</t>
+    <t>car-032-2.webp</t>
   </si>
   <si>
     <t>3rd gen H6 facelift (stated in title), China. Confirm it matches the Middle East 2026 H6 face.</t>
-  </si>
-  <si>
-    <t>Haval H6 III facelift 001.jpg</t>
-  </si>
-  <si>
-    <t>car-032-2.webp</t>
-  </si>
-  <si>
-    <t>Same series as car-032-1.</t>
   </si>
   <si>
     <t>2024 Hyundai Santa Fe Calligraphy AWD in Rockwood Green Pearl, front right.jpg</t>
@@ -4280,7 +4199,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J99"/>
+  <dimension ref="A1:J92"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -4369,13 +4288,13 @@
         <v>205</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="G3" s="11" t="s">
         <v>201</v>
@@ -4384,10 +4303,10 @@
         <v>202</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -4398,16 +4317,16 @@
         <v>196</v>
       </c>
       <c r="C4" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="F4" s="7" t="s">
         <v>208</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>210</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>211</v>
       </c>
       <c r="G4" s="11" t="s">
         <v>201</v>
@@ -4436,22 +4355,22 @@
         <v>216</v>
       </c>
       <c r="E5" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="F5" s="7" t="s">
         <v>217</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="G5" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="H5" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="I5" s="6" t="s">
         <v>218</v>
       </c>
-      <c r="G5" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="H5" s="11" t="s">
-        <v>202</v>
-      </c>
-      <c r="I5" s="6" t="s">
+      <c r="J5" s="7" t="s">
         <v>219</v>
-      </c>
-      <c r="J5" s="7" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -4462,16 +4381,16 @@
         <v>214</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>222</v>
+        <v>198</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>199</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>223</v>
+        <v>200</v>
       </c>
       <c r="G6" s="11" t="s">
         <v>201</v>
@@ -4480,10 +4399,10 @@
         <v>202</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -4494,16 +4413,16 @@
         <v>214</v>
       </c>
       <c r="C7" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="F7" s="7" t="s">
         <v>226</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>210</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>211</v>
       </c>
       <c r="G7" s="11" t="s">
         <v>201</v>
@@ -4532,7 +4451,7 @@
         <v>231</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>232</v>
@@ -4628,7 +4547,7 @@
         <v>248</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="F11" s="7" t="s">
         <v>249</v>
@@ -4660,7 +4579,7 @@
         <v>248</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>249</v>
@@ -4680,22 +4599,22 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="G13" s="11" t="s">
         <v>201</v>
@@ -4704,10 +4623,10 @@
         <v>202</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
@@ -4715,31 +4634,31 @@
         <v>60</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="C14" s="7" t="s">
         <v>261</v>
       </c>
       <c r="D14" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="G14" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="H14" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="I14" s="6" t="s">
         <v>262</v>
       </c>
-      <c r="E14" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="F14" s="7" t="s">
+      <c r="J14" s="7" t="s">
         <v>263</v>
-      </c>
-      <c r="G14" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="H14" s="11" t="s">
-        <v>202</v>
-      </c>
-      <c r="I14" s="6" t="s">
-        <v>264</v>
-      </c>
-      <c r="J14" s="7" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
@@ -4747,63 +4666,63 @@
         <v>60</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="C15" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="G15" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="H15" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="I15" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="J15" s="7" t="s">
         <v>266</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>262</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>263</v>
-      </c>
-      <c r="G15" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="H15" s="11" t="s">
-        <v>202</v>
-      </c>
-      <c r="I15" s="6" t="s">
-        <v>267</v>
-      </c>
-      <c r="J15" s="7" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="C16" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="G16" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="H16" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="I16" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="D16" s="6" t="s">
-        <v>262</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="F16" s="7" t="s">
-        <v>263</v>
-      </c>
-      <c r="G16" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="H16" s="11" t="s">
-        <v>202</v>
-      </c>
-      <c r="I16" s="6" t="s">
+      <c r="J16" s="7" t="s">
         <v>270</v>
-      </c>
-      <c r="J16" s="7" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
@@ -4811,19 +4730,19 @@
         <v>66</v>
       </c>
       <c r="B17" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="D17" s="6" t="s">
         <v>272</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>273</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>198</v>
       </c>
       <c r="E17" s="6" t="s">
         <v>199</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>200</v>
+        <v>273</v>
       </c>
       <c r="G17" s="11" t="s">
         <v>201</v>
@@ -4843,51 +4762,51 @@
         <v>66</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="C18" s="7" t="s">
         <v>276</v>
       </c>
       <c r="D18" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>273</v>
+      </c>
+      <c r="G18" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="H18" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="I18" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="E18" s="6" t="s">
-        <v>210</v>
-      </c>
-      <c r="F18" s="7" t="s">
+      <c r="J18" s="7" t="s">
         <v>278</v>
-      </c>
-      <c r="G18" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="H18" s="11" t="s">
-        <v>202</v>
-      </c>
-      <c r="I18" s="6" t="s">
-        <v>279</v>
-      </c>
-      <c r="J18" s="7" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>272</v>
+        <v>70</v>
       </c>
       <c r="C19" s="7" t="s">
+        <v>279</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="F19" s="7" t="s">
         <v>281</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>277</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>210</v>
-      </c>
-      <c r="F19" s="7" t="s">
-        <v>278</v>
       </c>
       <c r="G19" s="11" t="s">
         <v>201</v>
@@ -4913,25 +4832,25 @@
         <v>284</v>
       </c>
       <c r="D20" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>281</v>
+      </c>
+      <c r="G20" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="H20" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="I20" s="6" t="s">
         <v>285</v>
       </c>
-      <c r="E20" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="F20" s="7" t="s">
+      <c r="J20" s="7" t="s">
         <v>286</v>
-      </c>
-      <c r="G20" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="H20" s="11" t="s">
-        <v>202</v>
-      </c>
-      <c r="I20" s="6" t="s">
-        <v>287</v>
-      </c>
-      <c r="J20" s="7" t="s">
-        <v>288</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
@@ -4942,48 +4861,48 @@
         <v>70</v>
       </c>
       <c r="C21" s="7" t="s">
+        <v>287</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="G21" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="H21" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="I21" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="J21" s="7" t="s">
         <v>289</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>285</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="F21" s="7" t="s">
-        <v>286</v>
-      </c>
-      <c r="G21" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="H21" s="11" t="s">
-        <v>202</v>
-      </c>
-      <c r="I21" s="6" t="s">
-        <v>290</v>
-      </c>
-      <c r="J21" s="7" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="C22" s="7" t="s">
+        <v>290</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="F22" s="7" t="s">
         <v>292</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="E22" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="F22" s="7" t="s">
-        <v>200</v>
       </c>
       <c r="G22" s="11" t="s">
         <v>201</v>
@@ -5009,25 +4928,25 @@
         <v>295</v>
       </c>
       <c r="D23" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>292</v>
+      </c>
+      <c r="G23" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="H23" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="I23" s="6" t="s">
         <v>296</v>
       </c>
-      <c r="E23" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="F23" s="7" t="s">
+      <c r="J23" s="7" t="s">
         <v>297</v>
-      </c>
-      <c r="G23" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="H23" s="11" t="s">
-        <v>202</v>
-      </c>
-      <c r="I23" s="6" t="s">
-        <v>298</v>
-      </c>
-      <c r="J23" s="7" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
@@ -5038,16 +4957,16 @@
         <v>75</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>296</v>
+        <v>198</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>199</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>297</v>
+        <v>200</v>
       </c>
       <c r="G24" s="11" t="s">
         <v>201</v>
@@ -5056,30 +4975,30 @@
         <v>202</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="J24" s="7" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C25" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="F25" s="7" t="s">
         <v>303</v>
-      </c>
-      <c r="D25" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="E25" s="6" t="s">
-        <v>210</v>
-      </c>
-      <c r="F25" s="7" t="s">
-        <v>211</v>
       </c>
       <c r="G25" s="11" t="s">
         <v>201</v>
@@ -5105,25 +5024,25 @@
         <v>306</v>
       </c>
       <c r="D26" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>303</v>
+      </c>
+      <c r="G26" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="H26" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="I26" s="6" t="s">
         <v>307</v>
       </c>
-      <c r="E26" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="F26" s="7" t="s">
+      <c r="J26" s="7" t="s">
         <v>308</v>
-      </c>
-      <c r="G26" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="H26" s="11" t="s">
-        <v>202</v>
-      </c>
-      <c r="I26" s="6" t="s">
-        <v>309</v>
-      </c>
-      <c r="J26" s="7" t="s">
-        <v>310</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
@@ -5134,48 +5053,48 @@
         <v>78</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="F27" s="7" t="s">
+        <v>303</v>
+      </c>
+      <c r="G27" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="H27" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="I27" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="J27" s="7" t="s">
         <v>308</v>
-      </c>
-      <c r="G27" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="H27" s="11" t="s">
-        <v>202</v>
-      </c>
-      <c r="I27" s="6" t="s">
-        <v>312</v>
-      </c>
-      <c r="J27" s="7" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>78</v>
+        <v>311</v>
       </c>
       <c r="C28" s="7" t="s">
+        <v>312</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>313</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="F28" s="7" t="s">
         <v>314</v>
-      </c>
-      <c r="D28" s="6" t="s">
-        <v>307</v>
-      </c>
-      <c r="E28" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="F28" s="7" t="s">
-        <v>308</v>
       </c>
       <c r="G28" s="11" t="s">
         <v>201</v>
@@ -5187,7 +5106,7 @@
         <v>315</v>
       </c>
       <c r="J28" s="7" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
@@ -5195,51 +5114,51 @@
         <v>81</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="C29" s="7" t="s">
         <v>317</v>
       </c>
       <c r="D29" s="6" t="s">
+        <v>313</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="F29" s="7" t="s">
+        <v>314</v>
+      </c>
+      <c r="G29" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="H29" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="I29" s="6" t="s">
         <v>318</v>
       </c>
-      <c r="E29" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="F29" s="7" t="s">
+      <c r="J29" s="7" t="s">
         <v>319</v>
-      </c>
-      <c r="G29" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="H29" s="11" t="s">
-        <v>202</v>
-      </c>
-      <c r="I29" s="6" t="s">
-        <v>320</v>
-      </c>
-      <c r="J29" s="7" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="C30" s="7" t="s">
+        <v>321</v>
+      </c>
+      <c r="D30" s="6" t="s">
         <v>322</v>
       </c>
-      <c r="D30" s="6" t="s">
-        <v>318</v>
-      </c>
       <c r="E30" s="6" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="G30" s="11" t="s">
         <v>201</v>
@@ -5248,10 +5167,10 @@
         <v>202</v>
       </c>
       <c r="I30" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="J30" s="7" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
@@ -5259,31 +5178,31 @@
         <v>84</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="C31" s="7" t="s">
         <v>326</v>
       </c>
       <c r="D31" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="F31" s="7" t="s">
+        <v>323</v>
+      </c>
+      <c r="G31" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="H31" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="I31" s="6" t="s">
         <v>327</v>
       </c>
-      <c r="E31" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="F31" s="7" t="s">
+      <c r="J31" s="7" t="s">
         <v>328</v>
-      </c>
-      <c r="G31" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="H31" s="11" t="s">
-        <v>202</v>
-      </c>
-      <c r="I31" s="6" t="s">
-        <v>329</v>
-      </c>
-      <c r="J31" s="7" t="s">
-        <v>330</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
@@ -5291,19 +5210,19 @@
         <v>84</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="C32" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>330</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="F32" s="7" t="s">
         <v>331</v>
-      </c>
-      <c r="D32" s="6" t="s">
-        <v>327</v>
-      </c>
-      <c r="E32" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="F32" s="7" t="s">
-        <v>328</v>
       </c>
       <c r="G32" s="11" t="s">
         <v>201</v>
@@ -5320,34 +5239,34 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>325</v>
+        <v>334</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>335</v>
+        <v>248</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="F33" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="G33" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="H33" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="I33" s="6" t="s">
         <v>336</v>
       </c>
-      <c r="G33" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="H33" s="11" t="s">
-        <v>202</v>
-      </c>
-      <c r="I33" s="6" t="s">
+      <c r="J33" s="7" t="s">
         <v>337</v>
-      </c>
-      <c r="J33" s="7" t="s">
-        <v>338</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
@@ -5355,31 +5274,31 @@
         <v>88</v>
       </c>
       <c r="B34" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D34" s="6" t="s">
         <v>339</v>
       </c>
-      <c r="C34" s="7" t="s">
+      <c r="E34" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="F34" s="7" t="s">
         <v>340</v>
       </c>
-      <c r="D34" s="6" t="s">
+      <c r="G34" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="H34" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="I34" s="6" t="s">
         <v>341</v>
       </c>
-      <c r="E34" s="6" t="s">
-        <v>210</v>
-      </c>
-      <c r="F34" s="7" t="s">
+      <c r="J34" s="7" t="s">
         <v>342</v>
-      </c>
-      <c r="G34" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="H34" s="11" t="s">
-        <v>202</v>
-      </c>
-      <c r="I34" s="6" t="s">
-        <v>343</v>
-      </c>
-      <c r="J34" s="7" t="s">
-        <v>344</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
@@ -5387,16 +5306,16 @@
         <v>88</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D35" s="6" t="s">
         <v>248</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="F35" s="7" t="s">
         <v>249</v>
@@ -5408,30 +5327,30 @@
         <v>202</v>
       </c>
       <c r="I35" s="6" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="J35" s="7" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>339</v>
+        <v>94</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>248</v>
+        <v>198</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>199</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>249</v>
+        <v>200</v>
       </c>
       <c r="G36" s="11" t="s">
         <v>201</v>
@@ -5440,10 +5359,10 @@
         <v>202</v>
       </c>
       <c r="I36" s="6" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="J36" s="7" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
@@ -5454,28 +5373,28 @@
         <v>94</v>
       </c>
       <c r="C37" s="7" t="s">
+        <v>349</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="E37" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="F37" s="7" t="s">
         <v>351</v>
       </c>
-      <c r="D37" s="6" t="s">
+      <c r="G37" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="H37" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="I37" s="6" t="s">
         <v>352</v>
       </c>
-      <c r="E37" s="6" t="s">
+      <c r="J37" s="7" t="s">
         <v>353</v>
-      </c>
-      <c r="F37" s="7" t="s">
-        <v>354</v>
-      </c>
-      <c r="G37" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="H37" s="11" t="s">
-        <v>202</v>
-      </c>
-      <c r="I37" s="6" t="s">
-        <v>355</v>
-      </c>
-      <c r="J37" s="7" t="s">
-        <v>356</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
@@ -5486,16 +5405,16 @@
         <v>94</v>
       </c>
       <c r="C38" s="7" t="s">
+        <v>354</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>356</v>
+      </c>
+      <c r="F38" s="7" t="s">
         <v>357</v>
-      </c>
-      <c r="D38" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="E38" s="6" t="s">
-        <v>210</v>
-      </c>
-      <c r="F38" s="7" t="s">
-        <v>211</v>
       </c>
       <c r="G38" s="11" t="s">
         <v>201</v>
@@ -5512,34 +5431,34 @@
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>94</v>
+        <v>360</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>361</v>
+        <v>206</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="F39" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="G39" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="H39" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="I39" s="6" t="s">
         <v>362</v>
       </c>
-      <c r="G39" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="H39" s="11" t="s">
-        <v>202</v>
-      </c>
-      <c r="I39" s="6" t="s">
+      <c r="J39" s="7" t="s">
         <v>363</v>
-      </c>
-      <c r="J39" s="7" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
@@ -5547,63 +5466,63 @@
         <v>98</v>
       </c>
       <c r="B40" s="6" t="s">
+        <v>360</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>364</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="E40" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="F40" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="G40" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="H40" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="I40" s="6" t="s">
         <v>365</v>
       </c>
-      <c r="C40" s="7" t="s">
+      <c r="J40" s="7" t="s">
         <v>366</v>
-      </c>
-      <c r="D40" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="E40" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="F40" s="7" t="s">
-        <v>200</v>
-      </c>
-      <c r="G40" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="H40" s="11" t="s">
-        <v>202</v>
-      </c>
-      <c r="I40" s="6" t="s">
-        <v>367</v>
-      </c>
-      <c r="J40" s="7" t="s">
-        <v>368</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="6" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C41" s="7" t="s">
+        <v>368</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="F41" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="G41" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="H41" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="I41" s="6" t="s">
         <v>369</v>
       </c>
-      <c r="D41" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="E41" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="F41" s="7" t="s">
-        <v>200</v>
-      </c>
-      <c r="G41" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="H41" s="11" t="s">
-        <v>202</v>
-      </c>
-      <c r="I41" s="6" t="s">
+      <c r="J41" s="7" t="s">
         <v>370</v>
-      </c>
-      <c r="J41" s="7" t="s">
-        <v>371</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
@@ -5611,31 +5530,31 @@
         <v>102</v>
       </c>
       <c r="B42" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>371</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="F42" s="7" t="s">
+        <v>281</v>
+      </c>
+      <c r="G42" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="H42" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="I42" s="6" t="s">
         <v>372</v>
       </c>
-      <c r="C42" s="7" t="s">
+      <c r="J42" s="7" t="s">
         <v>373</v>
-      </c>
-      <c r="D42" s="6" t="s">
-        <v>285</v>
-      </c>
-      <c r="E42" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="F42" s="7" t="s">
-        <v>286</v>
-      </c>
-      <c r="G42" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="H42" s="11" t="s">
-        <v>202</v>
-      </c>
-      <c r="I42" s="6" t="s">
-        <v>374</v>
-      </c>
-      <c r="J42" s="7" t="s">
-        <v>375</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
@@ -5643,51 +5562,51 @@
         <v>102</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="C43" s="7" t="s">
+        <v>374</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="E43" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="F43" s="7" t="s">
+        <v>281</v>
+      </c>
+      <c r="G43" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="H43" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="I43" s="6" t="s">
+        <v>375</v>
+      </c>
+      <c r="J43" s="7" t="s">
         <v>376</v>
-      </c>
-      <c r="D43" s="6" t="s">
-        <v>285</v>
-      </c>
-      <c r="E43" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="F43" s="7" t="s">
-        <v>286</v>
-      </c>
-      <c r="G43" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="H43" s="11" t="s">
-        <v>202</v>
-      </c>
-      <c r="I43" s="6" t="s">
-        <v>377</v>
-      </c>
-      <c r="J43" s="7" t="s">
-        <v>378</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="6" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>372</v>
+        <v>107</v>
       </c>
       <c r="C44" s="7" t="s">
+        <v>377</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>378</v>
+      </c>
+      <c r="E44" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="F44" s="7" t="s">
         <v>379</v>
-      </c>
-      <c r="D44" s="6" t="s">
-        <v>248</v>
-      </c>
-      <c r="E44" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="F44" s="7" t="s">
-        <v>249</v>
       </c>
       <c r="G44" s="11" t="s">
         <v>201</v>
@@ -5713,77 +5632,77 @@
         <v>382</v>
       </c>
       <c r="D45" s="6" t="s">
+        <v>378</v>
+      </c>
+      <c r="E45" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="F45" s="7" t="s">
+        <v>379</v>
+      </c>
+      <c r="G45" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="H45" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="I45" s="6" t="s">
         <v>383</v>
       </c>
-      <c r="E45" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="F45" s="7" t="s">
+      <c r="J45" s="7" t="s">
         <v>384</v>
-      </c>
-      <c r="G45" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="H45" s="11" t="s">
-        <v>202</v>
-      </c>
-      <c r="I45" s="6" t="s">
-        <v>385</v>
-      </c>
-      <c r="J45" s="7" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C46" s="7" t="s">
+        <v>385</v>
+      </c>
+      <c r="D46" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="E46" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="F46" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="G46" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="H46" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="I46" s="6" t="s">
+        <v>386</v>
+      </c>
+      <c r="J46" s="7" t="s">
         <v>387</v>
-      </c>
-      <c r="D46" s="6" t="s">
-        <v>388</v>
-      </c>
-      <c r="E46" s="6" t="s">
-        <v>210</v>
-      </c>
-      <c r="F46" s="7" t="s">
-        <v>389</v>
-      </c>
-      <c r="G46" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="H46" s="11" t="s">
-        <v>202</v>
-      </c>
-      <c r="I46" s="6" t="s">
-        <v>390</v>
-      </c>
-      <c r="J46" s="7" t="s">
-        <v>391</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="6" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>383</v>
+        <v>224</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>199</v>
+        <v>225</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>384</v>
+        <v>226</v>
       </c>
       <c r="G47" s="11" t="s">
         <v>201</v>
@@ -5792,10 +5711,10 @@
         <v>202</v>
       </c>
       <c r="I47" s="6" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="J47" s="7" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
@@ -5806,16 +5725,16 @@
         <v>111</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>216</v>
+        <v>198</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>217</v>
+        <v>199</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>218</v>
+        <v>200</v>
       </c>
       <c r="G48" s="11" t="s">
         <v>201</v>
@@ -5824,30 +5743,30 @@
         <v>202</v>
       </c>
       <c r="I48" s="6" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="J48" s="7" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="6" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>111</v>
+        <v>394</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>216</v>
+        <v>302</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>218</v>
+        <v>303</v>
       </c>
       <c r="G49" s="11" t="s">
         <v>201</v>
@@ -5856,30 +5775,30 @@
         <v>202</v>
       </c>
       <c r="I49" s="6" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="J49" s="7" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>111</v>
+        <v>394</v>
       </c>
       <c r="C50" s="7" t="s">
+        <v>398</v>
+      </c>
+      <c r="D50" s="6" t="s">
+        <v>399</v>
+      </c>
+      <c r="E50" s="6" t="s">
+        <v>400</v>
+      </c>
+      <c r="F50" s="7" t="s">
         <v>401</v>
-      </c>
-      <c r="D50" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="E50" s="6" t="s">
-        <v>210</v>
-      </c>
-      <c r="F50" s="7" t="s">
-        <v>211</v>
       </c>
       <c r="G50" s="11" t="s">
         <v>201</v>
@@ -5896,7 +5815,7 @@
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="6" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B51" s="6" t="s">
         <v>404</v>
@@ -5905,45 +5824,45 @@
         <v>405</v>
       </c>
       <c r="D51" s="6" t="s">
+        <v>399</v>
+      </c>
+      <c r="E51" s="6" t="s">
+        <v>400</v>
+      </c>
+      <c r="F51" s="7" t="s">
+        <v>401</v>
+      </c>
+      <c r="G51" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="H51" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="I51" s="6" t="s">
         <v>406</v>
       </c>
-      <c r="E51" s="6" t="s">
+      <c r="J51" s="7" t="s">
         <v>407</v>
-      </c>
-      <c r="F51" s="7" t="s">
-        <v>408</v>
-      </c>
-      <c r="G51" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="H51" s="11" t="s">
-        <v>202</v>
-      </c>
-      <c r="I51" s="6" t="s">
-        <v>409</v>
-      </c>
-      <c r="J51" s="7" t="s">
-        <v>410</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B52" s="6" t="s">
         <v>404</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>406</v>
+        <v>399</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="F52" s="7" t="s">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="G52" s="11" t="s">
         <v>201</v>
@@ -5952,30 +5871,30 @@
         <v>202</v>
       </c>
       <c r="I52" s="6" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="J52" s="7" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" s="6" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B53" s="6" t="s">
         <v>404</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>307</v>
+        <v>412</v>
       </c>
       <c r="E53" s="6" t="s">
         <v>199</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>308</v>
+        <v>413</v>
       </c>
       <c r="G53" s="11" t="s">
         <v>201</v>
@@ -5984,318 +5903,318 @@
         <v>202</v>
       </c>
       <c r="I53" s="6" t="s">
+        <v>414</v>
+      </c>
+      <c r="J53" s="7" t="s">
         <v>415</v>
-      </c>
-      <c r="J53" s="7" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" s="6" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="B54" s="6" t="s">
+        <v>416</v>
+      </c>
+      <c r="C54" s="7" t="s">
         <v>417</v>
       </c>
-      <c r="C54" s="7" t="s">
+      <c r="D54" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="E54" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="F54" s="7" t="s">
+        <v>303</v>
+      </c>
+      <c r="G54" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="H54" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="I54" s="6" t="s">
         <v>418</v>
       </c>
-      <c r="D54" s="6" t="s">
-        <v>406</v>
-      </c>
-      <c r="E54" s="6" t="s">
-        <v>407</v>
-      </c>
-      <c r="F54" s="7" t="s">
-        <v>408</v>
-      </c>
-      <c r="G54" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="H54" s="11" t="s">
-        <v>202</v>
-      </c>
-      <c r="I54" s="6" t="s">
+      <c r="J54" s="7" t="s">
         <v>419</v>
-      </c>
-      <c r="J54" s="7" t="s">
-        <v>420</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" s="6" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C55" s="7" t="s">
+        <v>420</v>
+      </c>
+      <c r="D55" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="E55" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="F55" s="7" t="s">
+        <v>303</v>
+      </c>
+      <c r="G55" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="H55" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="I55" s="6" t="s">
         <v>421</v>
       </c>
-      <c r="D55" s="6" t="s">
-        <v>406</v>
-      </c>
-      <c r="E55" s="6" t="s">
-        <v>407</v>
-      </c>
-      <c r="F55" s="7" t="s">
-        <v>408</v>
-      </c>
-      <c r="G55" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="H55" s="11" t="s">
-        <v>202</v>
-      </c>
-      <c r="I55" s="6" t="s">
+      <c r="J55" s="7" t="s">
         <v>422</v>
-      </c>
-      <c r="J55" s="7" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" s="6" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C56" s="7" t="s">
+        <v>423</v>
+      </c>
+      <c r="D56" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="E56" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="F56" s="7" t="s">
+        <v>303</v>
+      </c>
+      <c r="G56" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="H56" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="I56" s="6" t="s">
         <v>424</v>
       </c>
-      <c r="D56" s="6" t="s">
-        <v>388</v>
-      </c>
-      <c r="E56" s="6" t="s">
-        <v>210</v>
-      </c>
-      <c r="F56" s="7" t="s">
-        <v>389</v>
-      </c>
-      <c r="G56" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="H56" s="11" t="s">
-        <v>202</v>
-      </c>
-      <c r="I56" s="6" t="s">
+      <c r="J56" s="7" t="s">
         <v>425</v>
-      </c>
-      <c r="J56" s="7" t="s">
-        <v>426</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="6" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="B57" s="6" t="s">
+        <v>426</v>
+      </c>
+      <c r="C57" s="7" t="s">
         <v>427</v>
       </c>
-      <c r="C57" s="7" t="s">
+      <c r="D57" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="E57" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="F57" s="7" t="s">
+        <v>303</v>
+      </c>
+      <c r="G57" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="H57" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="I57" s="6" t="s">
         <v>428</v>
       </c>
-      <c r="D57" s="6" t="s">
-        <v>307</v>
-      </c>
-      <c r="E57" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="F57" s="7" t="s">
-        <v>308</v>
-      </c>
-      <c r="G57" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="H57" s="11" t="s">
-        <v>202</v>
-      </c>
-      <c r="I57" s="6" t="s">
+      <c r="J57" s="7" t="s">
         <v>429</v>
-      </c>
-      <c r="J57" s="7" t="s">
-        <v>430</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" s="6" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C58" s="7" t="s">
+        <v>430</v>
+      </c>
+      <c r="D58" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="E58" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="F58" s="7" t="s">
+        <v>303</v>
+      </c>
+      <c r="G58" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="H58" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="I58" s="6" t="s">
         <v>431</v>
       </c>
-      <c r="D58" s="6" t="s">
-        <v>307</v>
-      </c>
-      <c r="E58" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="F58" s="7" t="s">
-        <v>308</v>
-      </c>
-      <c r="G58" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="H58" s="11" t="s">
-        <v>202</v>
-      </c>
-      <c r="I58" s="6" t="s">
+      <c r="J58" s="7" t="s">
         <v>432</v>
-      </c>
-      <c r="J58" s="7" t="s">
-        <v>433</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" s="6" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C59" s="7" t="s">
+        <v>433</v>
+      </c>
+      <c r="D59" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="E59" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="F59" s="7" t="s">
+        <v>303</v>
+      </c>
+      <c r="G59" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="H59" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="I59" s="6" t="s">
         <v>434</v>
       </c>
-      <c r="D59" s="6" t="s">
-        <v>307</v>
-      </c>
-      <c r="E59" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="F59" s="7" t="s">
-        <v>308</v>
-      </c>
-      <c r="G59" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="H59" s="11" t="s">
-        <v>202</v>
-      </c>
-      <c r="I59" s="6" t="s">
-        <v>435</v>
-      </c>
       <c r="J59" s="7" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" s="6" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B60" s="6" t="s">
+        <v>435</v>
+      </c>
+      <c r="C60" s="7" t="s">
+        <v>436</v>
+      </c>
+      <c r="D60" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="E60" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="F60" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="G60" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="H60" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="I60" s="6" t="s">
         <v>437</v>
       </c>
-      <c r="C60" s="7" t="s">
+      <c r="J60" s="7" t="s">
         <v>438</v>
-      </c>
-      <c r="D60" s="6" t="s">
-        <v>307</v>
-      </c>
-      <c r="E60" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="F60" s="7" t="s">
-        <v>308</v>
-      </c>
-      <c r="G60" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="H60" s="11" t="s">
-        <v>202</v>
-      </c>
-      <c r="I60" s="6" t="s">
-        <v>439</v>
-      </c>
-      <c r="J60" s="7" t="s">
-        <v>440</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" s="6" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C61" s="7" t="s">
+        <v>439</v>
+      </c>
+      <c r="D61" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="E61" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="F61" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="G61" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="H61" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="I61" s="6" t="s">
+        <v>440</v>
+      </c>
+      <c r="J61" s="7" t="s">
         <v>441</v>
-      </c>
-      <c r="D61" s="6" t="s">
-        <v>307</v>
-      </c>
-      <c r="E61" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="F61" s="7" t="s">
-        <v>308</v>
-      </c>
-      <c r="G61" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="H61" s="11" t="s">
-        <v>202</v>
-      </c>
-      <c r="I61" s="6" t="s">
-        <v>442</v>
-      </c>
-      <c r="J61" s="7" t="s">
-        <v>443</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" s="6" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C62" s="7" t="s">
+        <v>442</v>
+      </c>
+      <c r="D62" s="6" t="s">
+        <v>330</v>
+      </c>
+      <c r="E62" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="F62" s="7" t="s">
+        <v>331</v>
+      </c>
+      <c r="G62" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="H62" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="I62" s="6" t="s">
+        <v>443</v>
+      </c>
+      <c r="J62" s="7" t="s">
         <v>444</v>
-      </c>
-      <c r="D62" s="6" t="s">
-        <v>307</v>
-      </c>
-      <c r="E62" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="F62" s="7" t="s">
-        <v>308</v>
-      </c>
-      <c r="G62" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="H62" s="11" t="s">
-        <v>202</v>
-      </c>
-      <c r="I62" s="6" t="s">
-        <v>445</v>
-      </c>
-      <c r="J62" s="7" t="s">
-        <v>443</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" s="6" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B63" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="C63" s="7" t="s">
         <v>446</v>
       </c>
-      <c r="C63" s="7" t="s">
+      <c r="D63" s="6" t="s">
         <v>447</v>
       </c>
-      <c r="D63" s="6" t="s">
-        <v>216</v>
-      </c>
       <c r="E63" s="6" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="F63" s="7" t="s">
-        <v>218</v>
+        <v>448</v>
       </c>
       <c r="G63" s="11" t="s">
         <v>201</v>
@@ -6304,30 +6223,30 @@
         <v>202</v>
       </c>
       <c r="I63" s="6" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="J63" s="7" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" s="6" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>446</v>
+        <v>141</v>
       </c>
       <c r="C64" s="7" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>216</v>
+        <v>350</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="F64" s="7" t="s">
-        <v>218</v>
+        <v>351</v>
       </c>
       <c r="G64" s="11" t="s">
         <v>201</v>
@@ -6336,30 +6255,30 @@
         <v>202</v>
       </c>
       <c r="I64" s="6" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="J64" s="7" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" s="6" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>446</v>
+        <v>141</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>335</v>
+        <v>350</v>
       </c>
       <c r="E65" s="6" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="F65" s="7" t="s">
-        <v>336</v>
+        <v>351</v>
       </c>
       <c r="G65" s="11" t="s">
         <v>201</v>
@@ -6368,94 +6287,94 @@
         <v>202</v>
       </c>
       <c r="I65" s="6" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="J65" s="7" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" s="6" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>456</v>
+        <v>141</v>
       </c>
       <c r="C66" s="7" t="s">
         <v>457</v>
       </c>
       <c r="D66" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="E66" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="F66" s="7" t="s">
+        <v>351</v>
+      </c>
+      <c r="G66" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="H66" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="I66" s="6" t="s">
         <v>458</v>
       </c>
-      <c r="E66" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="F66" s="7" t="s">
+      <c r="J66" s="7" t="s">
         <v>459</v>
-      </c>
-      <c r="G66" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="H66" s="11" t="s">
-        <v>202</v>
-      </c>
-      <c r="I66" s="6" t="s">
-        <v>460</v>
-      </c>
-      <c r="J66" s="7" t="s">
-        <v>461</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" s="6" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="C67" s="7" t="s">
+        <v>461</v>
+      </c>
+      <c r="D67" s="6" t="s">
+        <v>399</v>
+      </c>
+      <c r="E67" s="6" t="s">
+        <v>400</v>
+      </c>
+      <c r="F67" s="7" t="s">
+        <v>401</v>
+      </c>
+      <c r="G67" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="H67" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="I67" s="6" t="s">
         <v>462</v>
       </c>
-      <c r="D67" s="6" t="s">
+      <c r="J67" s="7" t="s">
         <v>463</v>
-      </c>
-      <c r="E67" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="F67" s="7" t="s">
-        <v>464</v>
-      </c>
-      <c r="G67" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="H67" s="11" t="s">
-        <v>202</v>
-      </c>
-      <c r="I67" s="6" t="s">
-        <v>465</v>
-      </c>
-      <c r="J67" s="7" t="s">
-        <v>466</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" s="6" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>468</v>
+        <v>399</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>199</v>
+        <v>400</v>
       </c>
       <c r="F68" s="7" t="s">
-        <v>469</v>
+        <v>401</v>
       </c>
       <c r="G68" s="11" t="s">
         <v>201</v>
@@ -6464,30 +6383,30 @@
         <v>202</v>
       </c>
       <c r="I68" s="6" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="J68" s="7" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" s="6" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>141</v>
+        <v>460</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>361</v>
+        <v>468</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="F69" s="7" t="s">
-        <v>362</v>
+        <v>469</v>
       </c>
       <c r="G69" s="11" t="s">
         <v>201</v>
@@ -6496,30 +6415,30 @@
         <v>202</v>
       </c>
       <c r="I69" s="6" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="J69" s="7" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" s="6" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>141</v>
+        <v>472</v>
       </c>
       <c r="C70" s="7" t="s">
+        <v>473</v>
+      </c>
+      <c r="D70" s="6" t="s">
+        <v>474</v>
+      </c>
+      <c r="E70" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="F70" s="7" t="s">
         <v>475</v>
-      </c>
-      <c r="D70" s="6" t="s">
-        <v>361</v>
-      </c>
-      <c r="E70" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="F70" s="7" t="s">
-        <v>362</v>
       </c>
       <c r="G70" s="11" t="s">
         <v>201</v>
@@ -6536,22 +6455,22 @@
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" s="6" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>141</v>
+        <v>472</v>
       </c>
       <c r="C71" s="7" t="s">
         <v>478</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>361</v>
+        <v>474</v>
       </c>
       <c r="E71" s="6" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="F71" s="7" t="s">
-        <v>362</v>
+        <v>475</v>
       </c>
       <c r="G71" s="11" t="s">
         <v>201</v>
@@ -6568,54 +6487,54 @@
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" s="6" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="B72" s="6" t="s">
+        <v>472</v>
+      </c>
+      <c r="C72" s="7" t="s">
         <v>481</v>
       </c>
-      <c r="C72" s="7" t="s">
+      <c r="D72" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="E72" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="F72" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="G72" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="H72" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="I72" s="6" t="s">
         <v>482</v>
       </c>
-      <c r="D72" s="6" t="s">
-        <v>406</v>
-      </c>
-      <c r="E72" s="6" t="s">
-        <v>407</v>
-      </c>
-      <c r="F72" s="7" t="s">
-        <v>408</v>
-      </c>
-      <c r="G72" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="H72" s="11" t="s">
-        <v>202</v>
-      </c>
-      <c r="I72" s="6" t="s">
+      <c r="J72" s="7" t="s">
         <v>483</v>
-      </c>
-      <c r="J72" s="7" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" s="6" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="C73" s="7" t="s">
         <v>485</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>406</v>
+        <v>468</v>
       </c>
       <c r="E73" s="6" t="s">
-        <v>407</v>
+        <v>207</v>
       </c>
       <c r="F73" s="7" t="s">
-        <v>408</v>
+        <v>469</v>
       </c>
       <c r="G73" s="11" t="s">
         <v>201</v>
@@ -6632,22 +6551,22 @@
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" s="6" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="C74" s="7" t="s">
         <v>488</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>458</v>
+        <v>468</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="F74" s="7" t="s">
-        <v>459</v>
+        <v>469</v>
       </c>
       <c r="G74" s="11" t="s">
         <v>201</v>
@@ -6664,54 +6583,54 @@
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" s="6" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="B75" s="6" t="s">
+        <v>484</v>
+      </c>
+      <c r="C75" s="7" t="s">
         <v>491</v>
       </c>
-      <c r="C75" s="7" t="s">
+      <c r="D75" s="6" t="s">
         <v>492</v>
       </c>
-      <c r="D75" s="6" t="s">
+      <c r="E75" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="F75" s="7" t="s">
         <v>493</v>
       </c>
-      <c r="E75" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="F75" s="7" t="s">
+      <c r="G75" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="H75" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="I75" s="6" t="s">
         <v>494</v>
       </c>
-      <c r="G75" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="H75" s="11" t="s">
-        <v>202</v>
-      </c>
-      <c r="I75" s="6" t="s">
+      <c r="J75" s="7" t="s">
         <v>495</v>
-      </c>
-      <c r="J75" s="7" t="s">
-        <v>496</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" s="6" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>491</v>
+        <v>160</v>
       </c>
       <c r="C76" s="7" t="s">
+        <v>496</v>
+      </c>
+      <c r="D76" s="6" t="s">
         <v>497</v>
       </c>
-      <c r="D76" s="6" t="s">
-        <v>493</v>
-      </c>
       <c r="E76" s="6" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="F76" s="7" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="G76" s="11" t="s">
         <v>201</v>
@@ -6720,30 +6639,30 @@
         <v>202</v>
       </c>
       <c r="I76" s="6" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="J76" s="7" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77" s="6" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>491</v>
+        <v>160</v>
       </c>
       <c r="C77" s="7" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>209</v>
+        <v>497</v>
       </c>
       <c r="E77" s="6" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="F77" s="7" t="s">
-        <v>211</v>
+        <v>498</v>
       </c>
       <c r="G77" s="11" t="s">
         <v>201</v>
@@ -6752,30 +6671,30 @@
         <v>202</v>
       </c>
       <c r="I77" s="6" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="J77" s="7" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78" s="6" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C78" s="7" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="F78" s="7" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G78" s="11" t="s">
         <v>201</v>
@@ -6784,30 +6703,30 @@
         <v>202</v>
       </c>
       <c r="I78" s="6" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="J78" s="7" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79" s="6" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C79" s="7" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>458</v>
+        <v>511</v>
       </c>
       <c r="E79" s="6" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="F79" s="7" t="s">
-        <v>459</v>
+        <v>512</v>
       </c>
       <c r="G79" s="11" t="s">
         <v>201</v>
@@ -6816,30 +6735,30 @@
         <v>202</v>
       </c>
       <c r="I79" s="6" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="J79" s="7" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80" s="6" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>503</v>
+        <v>169</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>458</v>
+        <v>231</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>199</v>
       </c>
       <c r="F80" s="7" t="s">
-        <v>459</v>
+        <v>232</v>
       </c>
       <c r="G80" s="11" t="s">
         <v>201</v>
@@ -6848,30 +6767,30 @@
         <v>202</v>
       </c>
       <c r="I80" s="6" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="J80" s="7" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81" s="6" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="C81" s="7" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="D81" s="6" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="E81" s="6" t="s">
         <v>199</v>
       </c>
       <c r="F81" s="7" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="G81" s="11" t="s">
         <v>201</v>
@@ -6880,30 +6799,30 @@
         <v>202</v>
       </c>
       <c r="I81" s="6" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="J81" s="7" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82" s="6" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="D82" s="6" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>199</v>
       </c>
       <c r="F82" s="7" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="G82" s="11" t="s">
         <v>201</v>
@@ -6912,30 +6831,30 @@
         <v>202</v>
       </c>
       <c r="I82" s="6" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="J82" s="7" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A83" s="6" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="D83" s="6" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="E83" s="6" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="F83" s="7" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="G83" s="11" t="s">
         <v>201</v>
@@ -6944,126 +6863,126 @@
         <v>202</v>
       </c>
       <c r="I83" s="6" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="J83" s="7" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84" s="6" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>528</v>
+        <v>175</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>530</v>
+        <v>519</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="F84" s="7" t="s">
+        <v>527</v>
+      </c>
+      <c r="G84" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="H84" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="I84" s="6" t="s">
         <v>531</v>
       </c>
-      <c r="G84" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="H84" s="11" t="s">
-        <v>202</v>
-      </c>
-      <c r="I84" s="6" t="s">
+      <c r="J84" s="7" t="s">
         <v>532</v>
-      </c>
-      <c r="J84" s="7" t="s">
-        <v>533</v>
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" s="6" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>528</v>
+        <v>175</v>
       </c>
       <c r="C85" s="7" t="s">
+        <v>533</v>
+      </c>
+      <c r="D85" s="6" t="s">
+        <v>519</v>
+      </c>
+      <c r="E85" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="F85" s="7" t="s">
+        <v>527</v>
+      </c>
+      <c r="G85" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="H85" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="I85" s="6" t="s">
         <v>534</v>
       </c>
-      <c r="D85" s="6" t="s">
-        <v>535</v>
-      </c>
-      <c r="E85" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="F85" s="7" t="s">
-        <v>536</v>
-      </c>
-      <c r="G85" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="H85" s="11" t="s">
-        <v>202</v>
-      </c>
-      <c r="I85" s="6" t="s">
-        <v>537</v>
-      </c>
       <c r="J85" s="7" t="s">
-        <v>538</v>
+        <v>532</v>
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A86" s="6" t="s">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>528</v>
+        <v>178</v>
       </c>
       <c r="C86" s="7" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="D86" s="6" t="s">
-        <v>535</v>
+        <v>519</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>199</v>
       </c>
       <c r="F86" s="7" t="s">
+        <v>520</v>
+      </c>
+      <c r="G86" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="H86" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="I86" s="6" t="s">
         <v>536</v>
       </c>
-      <c r="G86" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="H86" s="11" t="s">
-        <v>202</v>
-      </c>
-      <c r="I86" s="6" t="s">
-        <v>540</v>
-      </c>
       <c r="J86" s="7" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A87" s="6" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="C87" s="7" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>543</v>
+        <v>519</v>
       </c>
       <c r="E87" s="6" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="F87" s="7" t="s">
-        <v>544</v>
+        <v>520</v>
       </c>
       <c r="G87" s="11" t="s">
         <v>201</v>
@@ -7072,62 +6991,62 @@
         <v>202</v>
       </c>
       <c r="I87" s="6" t="s">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="J87" s="7" t="s">
-        <v>546</v>
+        <v>540</v>
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A88" s="6" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="D88" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="E88" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="F88" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="G88" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="H88" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="I88" s="6" t="s">
+        <v>542</v>
+      </c>
+      <c r="J88" s="7" t="s">
         <v>543</v>
-      </c>
-      <c r="E88" s="6" t="s">
-        <v>210</v>
-      </c>
-      <c r="F88" s="7" t="s">
-        <v>544</v>
-      </c>
-      <c r="G88" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="H88" s="11" t="s">
-        <v>202</v>
-      </c>
-      <c r="I88" s="6" t="s">
-        <v>548</v>
-      </c>
-      <c r="J88" s="7" t="s">
-        <v>549</v>
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A89" s="6" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>550</v>
+        <v>544</v>
       </c>
       <c r="D89" s="6" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="E89" s="6" t="s">
-        <v>210</v>
+        <v>225</v>
       </c>
       <c r="F89" s="7" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="G89" s="11" t="s">
         <v>201</v>
@@ -7136,30 +7055,30 @@
         <v>202</v>
       </c>
       <c r="I89" s="6" t="s">
-        <v>551</v>
+        <v>545</v>
       </c>
       <c r="J89" s="7" t="s">
-        <v>552</v>
+        <v>546</v>
       </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A90" s="6" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="C90" s="7" t="s">
-        <v>553</v>
+        <v>547</v>
       </c>
       <c r="D90" s="6" t="s">
-        <v>543</v>
+        <v>248</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="F90" s="7" t="s">
-        <v>554</v>
+        <v>249</v>
       </c>
       <c r="G90" s="11" t="s">
         <v>201</v>
@@ -7168,298 +7087,74 @@
         <v>202</v>
       </c>
       <c r="I90" s="6" t="s">
-        <v>555</v>
+        <v>548</v>
       </c>
       <c r="J90" s="7" t="s">
-        <v>556</v>
+        <v>549</v>
       </c>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A91" s="6" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="C91" s="7" t="s">
-        <v>557</v>
+        <v>550</v>
       </c>
       <c r="D91" s="6" t="s">
-        <v>543</v>
+        <v>551</v>
       </c>
       <c r="E91" s="6" t="s">
         <v>199</v>
       </c>
       <c r="F91" s="7" t="s">
+        <v>552</v>
+      </c>
+      <c r="G91" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="H91" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="I91" s="6" t="s">
+        <v>553</v>
+      </c>
+      <c r="J91" s="7" t="s">
         <v>554</v>
-      </c>
-      <c r="G91" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="H91" s="11" t="s">
-        <v>202</v>
-      </c>
-      <c r="I91" s="6" t="s">
-        <v>558</v>
-      </c>
-      <c r="J91" s="7" t="s">
-        <v>559</v>
       </c>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A92" s="6" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="C92" s="7" t="s">
+        <v>555</v>
+      </c>
+      <c r="D92" s="6" t="s">
+        <v>556</v>
+      </c>
+      <c r="E92" s="6" t="s">
+        <v>557</v>
+      </c>
+      <c r="F92" s="7" t="s">
+        <v>558</v>
+      </c>
+      <c r="G92" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="H92" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="I92" s="6" t="s">
+        <v>559</v>
+      </c>
+      <c r="J92" s="7" t="s">
         <v>560</v>
-      </c>
-      <c r="D92" s="6" t="s">
-        <v>543</v>
-      </c>
-      <c r="E92" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="F92" s="7" t="s">
-        <v>554</v>
-      </c>
-      <c r="G92" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="H92" s="11" t="s">
-        <v>202</v>
-      </c>
-      <c r="I92" s="6" t="s">
-        <v>561</v>
-      </c>
-      <c r="J92" s="7" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A93" s="6" t="s">
-        <v>177</v>
-      </c>
-      <c r="B93" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="C93" s="7" t="s">
-        <v>562</v>
-      </c>
-      <c r="D93" s="6" t="s">
-        <v>543</v>
-      </c>
-      <c r="E93" s="6" t="s">
-        <v>210</v>
-      </c>
-      <c r="F93" s="7" t="s">
-        <v>544</v>
-      </c>
-      <c r="G93" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="H93" s="11" t="s">
-        <v>202</v>
-      </c>
-      <c r="I93" s="6" t="s">
-        <v>563</v>
-      </c>
-      <c r="J93" s="7" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A94" s="6" t="s">
-        <v>177</v>
-      </c>
-      <c r="B94" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="C94" s="7" t="s">
-        <v>565</v>
-      </c>
-      <c r="D94" s="6" t="s">
-        <v>543</v>
-      </c>
-      <c r="E94" s="6" t="s">
-        <v>210</v>
-      </c>
-      <c r="F94" s="7" t="s">
-        <v>544</v>
-      </c>
-      <c r="G94" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="H94" s="11" t="s">
-        <v>202</v>
-      </c>
-      <c r="I94" s="6" t="s">
-        <v>566</v>
-      </c>
-      <c r="J94" s="7" t="s">
-        <v>567</v>
-      </c>
-    </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A95" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="B95" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="C95" s="7" t="s">
-        <v>568</v>
-      </c>
-      <c r="D95" s="6" t="s">
-        <v>216</v>
-      </c>
-      <c r="E95" s="6" t="s">
-        <v>217</v>
-      </c>
-      <c r="F95" s="7" t="s">
-        <v>218</v>
-      </c>
-      <c r="G95" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="H95" s="11" t="s">
-        <v>202</v>
-      </c>
-      <c r="I95" s="6" t="s">
-        <v>569</v>
-      </c>
-      <c r="J95" s="7" t="s">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A96" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="B96" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="C96" s="7" t="s">
-        <v>571</v>
-      </c>
-      <c r="D96" s="6" t="s">
-        <v>216</v>
-      </c>
-      <c r="E96" s="6" t="s">
-        <v>217</v>
-      </c>
-      <c r="F96" s="7" t="s">
-        <v>218</v>
-      </c>
-      <c r="G96" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="H96" s="11" t="s">
-        <v>202</v>
-      </c>
-      <c r="I96" s="6" t="s">
-        <v>572</v>
-      </c>
-      <c r="J96" s="7" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A97" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="B97" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="C97" s="7" t="s">
-        <v>574</v>
-      </c>
-      <c r="D97" s="6" t="s">
-        <v>248</v>
-      </c>
-      <c r="E97" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="F97" s="7" t="s">
-        <v>249</v>
-      </c>
-      <c r="G97" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="H97" s="11" t="s">
-        <v>202</v>
-      </c>
-      <c r="I97" s="6" t="s">
-        <v>575</v>
-      </c>
-      <c r="J97" s="7" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A98" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="B98" s="6" t="s">
-        <v>186</v>
-      </c>
-      <c r="C98" s="7" t="s">
-        <v>577</v>
-      </c>
-      <c r="D98" s="6" t="s">
-        <v>578</v>
-      </c>
-      <c r="E98" s="6" t="s">
-        <v>210</v>
-      </c>
-      <c r="F98" s="7" t="s">
-        <v>579</v>
-      </c>
-      <c r="G98" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="H98" s="11" t="s">
-        <v>202</v>
-      </c>
-      <c r="I98" s="6" t="s">
-        <v>580</v>
-      </c>
-      <c r="J98" s="7" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A99" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="B99" s="6" t="s">
-        <v>186</v>
-      </c>
-      <c r="C99" s="7" t="s">
-        <v>582</v>
-      </c>
-      <c r="D99" s="6" t="s">
-        <v>583</v>
-      </c>
-      <c r="E99" s="6" t="s">
-        <v>584</v>
-      </c>
-      <c r="F99" s="7" t="s">
-        <v>585</v>
-      </c>
-      <c r="G99" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="H99" s="11" t="s">
-        <v>202</v>
-      </c>
-      <c r="I99" s="6" t="s">
-        <v>586</v>
-      </c>
-      <c r="J99" s="7" t="s">
-        <v>587</v>
       </c>
     </row>
   </sheetData>
@@ -7646,20 +7341,6 @@
     <hyperlink ref="H91" r:id="rId180"/>
     <hyperlink ref="G92" r:id="rId181"/>
     <hyperlink ref="H92" r:id="rId182"/>
-    <hyperlink ref="G93" r:id="rId183"/>
-    <hyperlink ref="H93" r:id="rId184"/>
-    <hyperlink ref="G94" r:id="rId185"/>
-    <hyperlink ref="H94" r:id="rId186"/>
-    <hyperlink ref="G95" r:id="rId187"/>
-    <hyperlink ref="H95" r:id="rId188"/>
-    <hyperlink ref="G96" r:id="rId189"/>
-    <hyperlink ref="H96" r:id="rId190"/>
-    <hyperlink ref="G97" r:id="rId191"/>
-    <hyperlink ref="H97" r:id="rId192"/>
-    <hyperlink ref="G98" r:id="rId193"/>
-    <hyperlink ref="H98" r:id="rId194"/>
-    <hyperlink ref="G99" r:id="rId195"/>
-    <hyperlink ref="H99" r:id="rId196"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -7678,90 +7359,90 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>588</v>
+        <v>561</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>589</v>
+        <v>562</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>590</v>
+        <v>563</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>591</v>
+        <v>564</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>592</v>
+        <v>565</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>593</v>
+        <v>566</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>594</v>
+        <v>567</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>595</v>
+        <v>568</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>596</v>
+        <v>569</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>597</v>
+        <v>570</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>598</v>
+        <v>571</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>599</v>
+        <v>572</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>600</v>
+        <v>573</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>601</v>
+        <v>574</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>602</v>
+        <v>575</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>603</v>
+        <v>576</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>604</v>
+        <v>577</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>605</v>
+        <v>578</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>606</v>
+        <v>579</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>607</v>
+        <v>580</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>608</v>
+        <v>581</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>609</v>
+        <v>582</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>610</v>
+        <v>583</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>611</v>
+        <v>584</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -7777,46 +7458,46 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>612</v>
+        <v>585</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>613</v>
+        <v>586</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>614</v>
+        <v>587</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>615</v>
+        <v>588</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>616</v>
+        <v>589</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>614</v>
+        <v>587</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>617</v>
+        <v>590</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>618</v>
+        <v>591</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>614</v>
+        <v>587</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>619</v>
+        <v>592</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>620</v>
+        <v>593</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>621</v>
+        <v>594</v>
       </c>
     </row>
   </sheetData>
